--- a/extra/report/No.課題2_テスト結果.xlsx.xlsx
+++ b/extra/report/No.課題2_テスト結果.xlsx.xlsx
@@ -3,23 +3,23 @@
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
   <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="20417"/>
   <workbookPr filterPrivacy="1" defaultThemeVersion="124226"/>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8D2A8C70-1BA4-435B-B7FA-DB12BDB88D3A}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BD498356-2F96-4BF4-BE0B-AC61997867E3}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="240" yWindow="105" windowWidth="14805" windowHeight="8010" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="240" yWindow="105" windowWidth="14805" windowHeight="8010" activeTab="4" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="前提" sheetId="2" r:id="rId1"/>
-    <sheet name="ケース1-2" sheetId="1" r:id="rId2"/>
-    <sheet name="ケース3-4" sheetId="3" r:id="rId3"/>
-    <sheet name="ケース5-6" sheetId="4" r:id="rId4"/>
-    <sheet name="ケース7-8" sheetId="5" r:id="rId5"/>
+    <sheet name="ケース1" sheetId="1" r:id="rId2"/>
+    <sheet name="ケース2" sheetId="3" r:id="rId3"/>
+    <sheet name="ケース3" sheetId="4" r:id="rId4"/>
+    <sheet name="ケース4" sheetId="5" r:id="rId5"/>
   </sheets>
   <calcPr calcId="152511"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="20" uniqueCount="15">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="17" uniqueCount="12">
   <si>
     <t>管理者アカウントでログイン済み</t>
     <phoneticPr fontId="1"/>
@@ -87,20 +87,6 @@
     <phoneticPr fontId="1"/>
   </si>
   <si>
-    <t>2.戻るを押下</t>
-    <rPh sb="2" eb="3">
-      <t>モド</t>
-    </rPh>
-    <rPh sb="5" eb="7">
-      <t>オウカ</t>
-    </rPh>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
-    <t>3.「メールアドレス」入力あり「氏名」空欄で検索ボタン押下</t>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
     <t>■詳細設計</t>
     <rPh sb="1" eb="3">
       <t>ショウサイ</t>
@@ -111,20 +97,6 @@
     <phoneticPr fontId="1"/>
   </si>
   <si>
-    <t>4.戻るを押下</t>
-    <rPh sb="2" eb="3">
-      <t>モド</t>
-    </rPh>
-    <rPh sb="5" eb="7">
-      <t>オウカ</t>
-    </rPh>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
-    <t>5.「メールアドレス」空欄「氏名」入力ありで検索ボタン押下</t>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
     <t>■詳細設計</t>
     <rPh sb="1" eb="5">
       <t>ショウサイセッケイ</t>
@@ -132,27 +104,25 @@
     <phoneticPr fontId="1"/>
   </si>
   <si>
-    <t>6.戻るを押下</t>
-    <rPh sb="2" eb="3">
-      <t>モド</t>
+    <t>データーベースに登録済みのユーザー情報が表示される</t>
+    <rPh sb="8" eb="11">
+      <t>トウロクズ</t>
     </rPh>
-    <rPh sb="5" eb="7">
-      <t>オウカ</t>
+    <rPh sb="20" eb="22">
+      <t>ヒョウジ</t>
     </rPh>
     <phoneticPr fontId="1"/>
   </si>
   <si>
-    <t>7.「メールアドレス」「氏名」両方入力ありで検索ボタン押下</t>
+    <t>3.「メールアドレス」空欄「氏名」入力ありで検索ボタン押下</t>
     <phoneticPr fontId="1"/>
   </si>
   <si>
-    <t>8.戻るを押下</t>
-    <rPh sb="2" eb="3">
-      <t>モド</t>
-    </rPh>
-    <rPh sb="5" eb="7">
-      <t>オウカ</t>
-    </rPh>
+    <t>2.「メールアドレス」入力あり「氏名」空欄で検索ボタン押下</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>4.「メールアドレス」「氏名」両方入力ありで検索ボタン押下</t>
     <phoneticPr fontId="1"/>
   </si>
 </sst>
@@ -160,7 +130,7 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="3" x14ac:knownFonts="1">
+  <fonts count="4" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -184,6 +154,13 @@
       <charset val="128"/>
       <scheme val="minor"/>
     </font>
+    <font>
+      <sz val="10"/>
+      <color theme="1"/>
+      <name val="游ゴシック"/>
+      <family val="3"/>
+      <charset val="128"/>
+    </font>
   </fonts>
   <fills count="2">
     <fill>
@@ -205,9 +182,12 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="justify" vertical="center"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="標準" xfId="0" builtinId="0"/>
@@ -633,6 +613,56 @@
     </xdr:pic>
     <xdr:clientData/>
   </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>1</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>46</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>15</xdr:col>
+      <xdr:colOff>416169</xdr:colOff>
+      <xdr:row>59</xdr:row>
+      <xdr:rowOff>73274</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="3" name="図 2">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{CAA6B59B-1878-4E7E-8E16-369B5B38A9CB}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId4" cstate="print">
+          <a:extLst>
+            <a:ext uri="{28A0092B-C50C-407E-A947-70E740481C1C}">
+              <a14:useLocalDpi xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" val="0"/>
+            </a:ext>
+          </a:extLst>
+        </a:blip>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="688731" y="7751885"/>
+          <a:ext cx="10058400" cy="2264024"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
 </xdr:wsDr>
 </file>
 
@@ -910,74 +940,6 @@
         </a:prstGeom>
       </xdr:spPr>
     </xdr:pic>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-  <xdr:twoCellAnchor>
-    <xdr:from>
-      <xdr:col>9</xdr:col>
-      <xdr:colOff>203639</xdr:colOff>
-      <xdr:row>30</xdr:row>
-      <xdr:rowOff>0</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>10</xdr:col>
-      <xdr:colOff>269328</xdr:colOff>
-      <xdr:row>31</xdr:row>
-      <xdr:rowOff>45982</xdr:rowOff>
-    </xdr:to>
-    <xdr:sp macro="" textlink="">
-      <xdr:nvSpPr>
-        <xdr:cNvPr id="16" name="正方形/長方形 15">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{9E945BB6-5F6B-437C-A61F-ED5D2423BF53}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvSpPr/>
-      </xdr:nvSpPr>
-      <xdr:spPr>
-        <a:xfrm>
-          <a:off x="2686708" y="5123793"/>
-          <a:ext cx="341586" cy="216775"/>
-        </a:xfrm>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-        <a:noFill/>
-        <a:ln w="38100" cap="flat" cmpd="sng" algn="ctr">
-          <a:solidFill>
-            <a:srgbClr val="FF0000"/>
-          </a:solidFill>
-          <a:prstDash val="solid"/>
-          <a:round/>
-          <a:headEnd type="none" w="med" len="med"/>
-          <a:tailEnd type="none" w="med" len="med"/>
-        </a:ln>
-      </xdr:spPr>
-      <xdr:style>
-        <a:lnRef idx="0">
-          <a:scrgbClr r="0" g="0" b="0"/>
-        </a:lnRef>
-        <a:fillRef idx="0">
-          <a:scrgbClr r="0" g="0" b="0"/>
-        </a:fillRef>
-        <a:effectRef idx="0">
-          <a:scrgbClr r="0" g="0" b="0"/>
-        </a:effectRef>
-        <a:fontRef idx="minor">
-          <a:schemeClr val="accent2"/>
-        </a:fontRef>
-      </xdr:style>
-      <xdr:txBody>
-        <a:bodyPr vertOverflow="clip" horzOverflow="clip" rtlCol="0" anchor="t"/>
-        <a:lstStyle/>
-        <a:p>
-          <a:pPr algn="l"/>
-          <a:endParaRPr kumimoji="1" lang="ja-JP" altLang="en-US" sz="1100"/>
-        </a:p>
-      </xdr:txBody>
-    </xdr:sp>
     <xdr:clientData/>
   </xdr:twoCellAnchor>
   <xdr:twoCellAnchor editAs="oneCell">
@@ -1107,7 +1069,31 @@
               <a:ea typeface="+mn-ea"/>
               <a:cs typeface="+mn-cs"/>
             </a:rPr>
-            <a:t>「メールアドレス」「氏名」両方空欄で検索ボタン押下したときに存在するユーザー情報が全権取得されて表示される</a:t>
+            <a:t>「メールアドレス」「氏名」両方空欄で検索ボタン押下したときに存在するユーザー情報が</a:t>
+          </a:r>
+          <a:r>
+            <a:rPr lang="ja-JP" altLang="en-US" sz="1100">
+              <a:solidFill>
+                <a:schemeClr val="dk1"/>
+              </a:solidFill>
+              <a:effectLst/>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:rPr>
+            <a:t>全件</a:t>
+          </a:r>
+          <a:r>
+            <a:rPr lang="ja-JP" altLang="ja-JP" sz="1100">
+              <a:solidFill>
+                <a:schemeClr val="dk1"/>
+              </a:solidFill>
+              <a:effectLst/>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:rPr>
+            <a:t>取得されて表示される</a:t>
           </a:r>
           <a:endParaRPr kumimoji="1" lang="ja-JP" altLang="en-US" sz="1100"/>
         </a:p>
@@ -1115,34 +1101,257 @@
     </xdr:sp>
     <xdr:clientData/>
   </xdr:twoCellAnchor>
+</xdr:wsDr>
+</file>
+
+<file path=xl/drawings/drawing3.xml><?xml version="1.0" encoding="utf-8"?>
+<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>0</xdr:col>
+      <xdr:colOff>683172</xdr:colOff>
+      <xdr:row>3</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>15</xdr:col>
+      <xdr:colOff>493986</xdr:colOff>
+      <xdr:row>12</xdr:row>
+      <xdr:rowOff>7586</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="3" name="図 2">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{EBF92EDC-507F-4A0F-9382-A1E35FB6CF22}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId1" cstate="print">
+          <a:extLst>
+            <a:ext uri="{28A0092B-C50C-407E-A947-70E740481C1C}">
+              <a14:useLocalDpi xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" val="0"/>
+            </a:ext>
+          </a:extLst>
+        </a:blip>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="683172" y="512379"/>
+          <a:ext cx="10058400" cy="1544724"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>17</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>3</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>22</xdr:col>
+      <xdr:colOff>249757</xdr:colOff>
+      <xdr:row>22</xdr:row>
+      <xdr:rowOff>151086</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="5" name="図 4">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{63538C4B-AC09-48ED-88E7-DFE58E4AC630}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId2">
+          <a:extLst>
+            <a:ext uri="{28A0092B-C50C-407E-A947-70E740481C1C}">
+              <a14:useLocalDpi xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" val="0"/>
+            </a:ext>
+          </a:extLst>
+        </a:blip>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="11613931" y="512379"/>
+          <a:ext cx="3665619" cy="3396155"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>17</xdr:col>
+      <xdr:colOff>6569</xdr:colOff>
+      <xdr:row>27</xdr:row>
+      <xdr:rowOff>6568</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>22</xdr:col>
+      <xdr:colOff>400706</xdr:colOff>
+      <xdr:row>58</xdr:row>
+      <xdr:rowOff>164874</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="7" name="図 6">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{3837003E-9B86-42F7-AFA2-E38AF0FC0645}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId3">
+          <a:extLst>
+            <a:ext uri="{28A0092B-C50C-407E-A947-70E740481C1C}">
+              <a14:useLocalDpi xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" val="0"/>
+            </a:ext>
+          </a:extLst>
+        </a:blip>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="11620500" y="4617982"/>
+          <a:ext cx="3809999" cy="5452892"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
   <xdr:twoCellAnchor>
     <xdr:from>
-      <xdr:col>10</xdr:col>
-      <xdr:colOff>78827</xdr:colOff>
-      <xdr:row>31</xdr:row>
-      <xdr:rowOff>118241</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>10</xdr:col>
-      <xdr:colOff>85396</xdr:colOff>
-      <xdr:row>58</xdr:row>
-      <xdr:rowOff>151086</xdr:rowOff>
+      <xdr:col>4</xdr:col>
+      <xdr:colOff>387569</xdr:colOff>
+      <xdr:row>9</xdr:row>
+      <xdr:rowOff>111673</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>5</xdr:col>
+      <xdr:colOff>45983</xdr:colOff>
+      <xdr:row>10</xdr:row>
+      <xdr:rowOff>157655</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="8" name="正方形/長方形 7">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{04268AEB-C43C-434C-A570-348B209499BF}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvSpPr/>
+      </xdr:nvSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="3120259" y="1648811"/>
+          <a:ext cx="341586" cy="216775"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:noFill/>
+        <a:ln w="38100" cap="flat" cmpd="sng" algn="ctr">
+          <a:solidFill>
+            <a:srgbClr val="FF0000"/>
+          </a:solidFill>
+          <a:prstDash val="solid"/>
+          <a:round/>
+          <a:headEnd type="none" w="med" len="med"/>
+          <a:tailEnd type="none" w="med" len="med"/>
+        </a:ln>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="0">
+          <a:scrgbClr r="0" g="0" b="0"/>
+        </a:lnRef>
+        <a:fillRef idx="0">
+          <a:scrgbClr r="0" g="0" b="0"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:scrgbClr r="0" g="0" b="0"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="accent2"/>
+        </a:fontRef>
+      </xdr:style>
+      <xdr:txBody>
+        <a:bodyPr vertOverflow="clip" horzOverflow="clip" rtlCol="0" anchor="t"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr algn="l"/>
+          <a:endParaRPr kumimoji="1" lang="ja-JP" altLang="en-US" sz="1100"/>
+        </a:p>
+      </xdr:txBody>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>4</xdr:col>
+      <xdr:colOff>558362</xdr:colOff>
+      <xdr:row>11</xdr:row>
+      <xdr:rowOff>32845</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>4</xdr:col>
+      <xdr:colOff>558362</xdr:colOff>
+      <xdr:row>25</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
     </xdr:to>
     <xdr:cxnSp macro="">
       <xdr:nvCxnSpPr>
-        <xdr:cNvPr id="21" name="直線矢印コネクタ 20">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{2A631286-EF08-4A70-BE4F-1AE8ADF996BC}"/>
+        <xdr:cNvPr id="9" name="直線矢印コネクタ 8">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{8B56B1F7-29CF-4215-AFD4-4B4341237CA9}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
         <xdr:cNvCxnSpPr/>
       </xdr:nvCxnSpPr>
       <xdr:spPr>
-        <a:xfrm flipH="1">
-          <a:off x="2837793" y="5412827"/>
-          <a:ext cx="6569" cy="4644259"/>
+        <a:xfrm>
+          <a:off x="3291052" y="1911569"/>
+          <a:ext cx="0" cy="2358259"/>
         </a:xfrm>
         <a:prstGeom prst="straightConnector1">
           <a:avLst/>
@@ -1173,23 +1382,23 @@
   </xdr:twoCellAnchor>
   <xdr:twoCellAnchor editAs="oneCell">
     <xdr:from>
-      <xdr:col>0</xdr:col>
-      <xdr:colOff>262759</xdr:colOff>
-      <xdr:row>59</xdr:row>
-      <xdr:rowOff>164224</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>37</xdr:col>
-      <xdr:colOff>112987</xdr:colOff>
-      <xdr:row>68</xdr:row>
-      <xdr:rowOff>137616</xdr:rowOff>
+      <xdr:col>1</xdr:col>
+      <xdr:colOff>6569</xdr:colOff>
+      <xdr:row>27</xdr:row>
+      <xdr:rowOff>19707</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>15</xdr:col>
+      <xdr:colOff>500555</xdr:colOff>
+      <xdr:row>38</xdr:row>
+      <xdr:rowOff>157379</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
-        <xdr:cNvPr id="25" name="図 24">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{6A1000A4-B690-4520-A1B2-4020C48D10CA}"/>
+        <xdr:cNvPr id="11" name="図 10">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{3478F6D2-C06D-4D9C-9DCC-E0C7E1AC33CC}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -1198,7 +1407,7 @@
         </xdr:cNvPicPr>
       </xdr:nvPicPr>
       <xdr:blipFill>
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId5" cstate="print">
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId4" cstate="print">
           <a:extLst>
             <a:ext uri="{28A0092B-C50C-407E-A947-70E740481C1C}">
               <a14:useLocalDpi xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" val="0"/>
@@ -1211,8 +1420,8 @@
       </xdr:blipFill>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="262759" y="10241017"/>
-          <a:ext cx="10058400" cy="1510530"/>
+          <a:off x="689741" y="4631121"/>
+          <a:ext cx="10058400" cy="2016396"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -1223,23 +1432,23 @@
   </xdr:twoCellAnchor>
   <xdr:twoCellAnchor>
     <xdr:from>
-      <xdr:col>17</xdr:col>
-      <xdr:colOff>39415</xdr:colOff>
-      <xdr:row>58</xdr:row>
+      <xdr:col>7</xdr:col>
+      <xdr:colOff>617482</xdr:colOff>
+      <xdr:row>23</xdr:row>
       <xdr:rowOff>59121</xdr:rowOff>
     </xdr:from>
     <xdr:to>
-      <xdr:col>26</xdr:col>
-      <xdr:colOff>6569</xdr:colOff>
-      <xdr:row>61</xdr:row>
-      <xdr:rowOff>111673</xdr:rowOff>
+      <xdr:col>13</xdr:col>
+      <xdr:colOff>216775</xdr:colOff>
+      <xdr:row>27</xdr:row>
+      <xdr:rowOff>39414</xdr:rowOff>
     </xdr:to>
     <xdr:sp macro="" textlink="">
       <xdr:nvSpPr>
-        <xdr:cNvPr id="28" name="吹き出し: 四角形 27">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{D55E6609-7B0A-4C7E-A0BD-E9ECAC861E9D}"/>
+        <xdr:cNvPr id="12" name="吹き出し: 四角形 11">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{3C48985B-30E2-4633-BB2E-28F0A4EC5362}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -1247,13 +1456,13 @@
       </xdr:nvSpPr>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="4729656" y="9965121"/>
-          <a:ext cx="2450223" cy="564931"/>
+          <a:off x="5399689" y="3987362"/>
+          <a:ext cx="3698327" cy="663466"/>
         </a:xfrm>
         <a:prstGeom prst="wedgeRectCallout">
           <a:avLst>
-            <a:gd name="adj1" fmla="val -32990"/>
-            <a:gd name="adj2" fmla="val 106764"/>
+            <a:gd name="adj1" fmla="val -39124"/>
+            <a:gd name="adj2" fmla="val 109120"/>
           </a:avLst>
         </a:prstGeom>
       </xdr:spPr>
@@ -1302,7 +1511,7 @@
               <a:ea typeface="+mn-ea"/>
               <a:cs typeface="+mn-cs"/>
             </a:rPr>
-            <a:t>NO2.</a:t>
+            <a:t>NO.2</a:t>
           </a:r>
           <a:r>
             <a:rPr lang="ja-JP" altLang="ja-JP" sz="1100">
@@ -1314,10 +1523,10 @@
               <a:ea typeface="+mn-ea"/>
               <a:cs typeface="+mn-cs"/>
             </a:rPr>
-            <a:t>戻るボタンを押下して</a:t>
+            <a:t>「メールアドレス」のみに</a:t>
           </a:r>
           <a:r>
-            <a:rPr lang="ja-JP" altLang="en-US" sz="1100">
+            <a:rPr lang="en-US" altLang="ja-JP" sz="1100">
               <a:solidFill>
                 <a:schemeClr val="dk1"/>
               </a:solidFill>
@@ -1326,7 +1535,7 @@
               <a:ea typeface="+mn-ea"/>
               <a:cs typeface="+mn-cs"/>
             </a:rPr>
-            <a:t>加入者情報</a:t>
+            <a:t>”a”</a:t>
           </a:r>
           <a:r>
             <a:rPr lang="ja-JP" altLang="ja-JP" sz="1100">
@@ -1338,10 +1547,10 @@
               <a:ea typeface="+mn-ea"/>
               <a:cs typeface="+mn-cs"/>
             </a:rPr>
-            <a:t>検索画面に戻</a:t>
+            <a:t>と入力して検索ボタンを押下したとき、</a:t>
           </a:r>
           <a:r>
-            <a:rPr lang="ja-JP" altLang="en-US" sz="1100">
+            <a:rPr lang="en-US" altLang="ja-JP" sz="1100">
               <a:solidFill>
                 <a:schemeClr val="dk1"/>
               </a:solidFill>
@@ -1350,17 +1559,20 @@
               <a:ea typeface="+mn-ea"/>
               <a:cs typeface="+mn-cs"/>
             </a:rPr>
-            <a:t>れる</a:t>
+            <a:t>”a”</a:t>
           </a:r>
-          <a:endParaRPr lang="ja-JP" altLang="ja-JP" sz="1100">
-            <a:solidFill>
-              <a:schemeClr val="dk1"/>
-            </a:solidFill>
-            <a:effectLst/>
-            <a:latin typeface="+mn-lt"/>
-            <a:ea typeface="+mn-ea"/>
-            <a:cs typeface="+mn-cs"/>
-          </a:endParaRPr>
+          <a:r>
+            <a:rPr lang="ja-JP" altLang="ja-JP" sz="1100">
+              <a:solidFill>
+                <a:schemeClr val="dk1"/>
+              </a:solidFill>
+              <a:effectLst/>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:rPr>
+            <a:t>と部分一致したメールアドレスを持つユーザーの情報が表示される</a:t>
+          </a:r>
         </a:p>
         <a:p>
           <a:pPr algn="l"/>
@@ -1373,27 +1585,27 @@
 </xdr:wsDr>
 </file>
 
-<file path=xl/drawings/drawing3.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/drawings/drawing4.xml><?xml version="1.0" encoding="utf-8"?>
 <xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
   <xdr:twoCellAnchor editAs="oneCell">
     <xdr:from>
-      <xdr:col>0</xdr:col>
-      <xdr:colOff>683172</xdr:colOff>
+      <xdr:col>1</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
       <xdr:row>3</xdr:row>
       <xdr:rowOff>0</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>15</xdr:col>
-      <xdr:colOff>493986</xdr:colOff>
-      <xdr:row>12</xdr:row>
-      <xdr:rowOff>7586</xdr:rowOff>
+      <xdr:colOff>457200</xdr:colOff>
+      <xdr:row>11</xdr:row>
+      <xdr:rowOff>102374</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
         <xdr:cNvPr id="3" name="図 2">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{EBF92EDC-507F-4A0F-9382-A1E35FB6CF22}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{3FB681B9-4082-49B7-BA0E-76B627168F5D}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -1415,8 +1627,8 @@
       </xdr:blipFill>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="683172" y="512379"/>
-          <a:ext cx="10058400" cy="1544724"/>
+          <a:off x="685800" y="514350"/>
+          <a:ext cx="10058400" cy="1473974"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -1428,22 +1640,22 @@
   <xdr:twoCellAnchor editAs="oneCell">
     <xdr:from>
       <xdr:col>17</xdr:col>
-      <xdr:colOff>0</xdr:colOff>
-      <xdr:row>3</xdr:row>
-      <xdr:rowOff>0</xdr:rowOff>
+      <xdr:colOff>6569</xdr:colOff>
+      <xdr:row>2</xdr:row>
+      <xdr:rowOff>144517</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>22</xdr:col>
-      <xdr:colOff>249757</xdr:colOff>
+      <xdr:colOff>157654</xdr:colOff>
       <xdr:row>22</xdr:row>
-      <xdr:rowOff>151086</xdr:rowOff>
+      <xdr:rowOff>34410</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
         <xdr:cNvPr id="5" name="図 4">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{63538C4B-AC09-48ED-88E7-DFE58E4AC630}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{381A5ABC-B53A-40DA-BD21-46EADC4CA750}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -1465,8 +1677,8 @@
       </xdr:blipFill>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="11613931" y="512379"/>
-          <a:ext cx="3665619" cy="3396155"/>
+          <a:off x="11620500" y="486103"/>
+          <a:ext cx="3566947" cy="3305755"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -1477,23 +1689,23 @@
   </xdr:twoCellAnchor>
   <xdr:twoCellAnchor editAs="oneCell">
     <xdr:from>
-      <xdr:col>17</xdr:col>
-      <xdr:colOff>6569</xdr:colOff>
-      <xdr:row>27</xdr:row>
-      <xdr:rowOff>6568</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>22</xdr:col>
-      <xdr:colOff>400706</xdr:colOff>
-      <xdr:row>58</xdr:row>
-      <xdr:rowOff>164874</xdr:rowOff>
+      <xdr:col>0</xdr:col>
+      <xdr:colOff>683172</xdr:colOff>
+      <xdr:row>26</xdr:row>
+      <xdr:rowOff>6569</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>15</xdr:col>
+      <xdr:colOff>493986</xdr:colOff>
+      <xdr:row>36</xdr:row>
+      <xdr:rowOff>587</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
         <xdr:cNvPr id="7" name="図 6">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{3837003E-9B86-42F7-AFA2-E38AF0FC0645}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{806FDD9E-5007-4DCB-82EE-554046F924ED}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -1502,7 +1714,7 @@
         </xdr:cNvPicPr>
       </xdr:nvPicPr>
       <xdr:blipFill>
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId3">
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId3" cstate="print">
           <a:extLst>
             <a:ext uri="{28A0092B-C50C-407E-A947-70E740481C1C}">
               <a14:useLocalDpi xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" val="0"/>
@@ -1515,8 +1727,8 @@
       </xdr:blipFill>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="11620500" y="4617982"/>
-          <a:ext cx="3809999" cy="5452892"/>
+          <a:off x="683172" y="4447190"/>
+          <a:ext cx="10058400" cy="1701949"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -1525,149 +1737,25 @@
     </xdr:pic>
     <xdr:clientData/>
   </xdr:twoCellAnchor>
-  <xdr:twoCellAnchor>
-    <xdr:from>
-      <xdr:col>4</xdr:col>
-      <xdr:colOff>387569</xdr:colOff>
-      <xdr:row>9</xdr:row>
-      <xdr:rowOff>111673</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>5</xdr:col>
-      <xdr:colOff>45983</xdr:colOff>
-      <xdr:row>10</xdr:row>
-      <xdr:rowOff>157655</xdr:rowOff>
-    </xdr:to>
-    <xdr:sp macro="" textlink="">
-      <xdr:nvSpPr>
-        <xdr:cNvPr id="8" name="正方形/長方形 7">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{04268AEB-C43C-434C-A570-348B209499BF}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvSpPr/>
-      </xdr:nvSpPr>
-      <xdr:spPr>
-        <a:xfrm>
-          <a:off x="3120259" y="1648811"/>
-          <a:ext cx="341586" cy="216775"/>
-        </a:xfrm>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-        <a:noFill/>
-        <a:ln w="38100" cap="flat" cmpd="sng" algn="ctr">
-          <a:solidFill>
-            <a:srgbClr val="FF0000"/>
-          </a:solidFill>
-          <a:prstDash val="solid"/>
-          <a:round/>
-          <a:headEnd type="none" w="med" len="med"/>
-          <a:tailEnd type="none" w="med" len="med"/>
-        </a:ln>
-      </xdr:spPr>
-      <xdr:style>
-        <a:lnRef idx="0">
-          <a:scrgbClr r="0" g="0" b="0"/>
-        </a:lnRef>
-        <a:fillRef idx="0">
-          <a:scrgbClr r="0" g="0" b="0"/>
-        </a:fillRef>
-        <a:effectRef idx="0">
-          <a:scrgbClr r="0" g="0" b="0"/>
-        </a:effectRef>
-        <a:fontRef idx="minor">
-          <a:schemeClr val="accent2"/>
-        </a:fontRef>
-      </xdr:style>
-      <xdr:txBody>
-        <a:bodyPr vertOverflow="clip" horzOverflow="clip" rtlCol="0" anchor="t"/>
-        <a:lstStyle/>
-        <a:p>
-          <a:pPr algn="l"/>
-          <a:endParaRPr kumimoji="1" lang="ja-JP" altLang="en-US" sz="1100"/>
-        </a:p>
-      </xdr:txBody>
-    </xdr:sp>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-  <xdr:twoCellAnchor>
-    <xdr:from>
-      <xdr:col>4</xdr:col>
-      <xdr:colOff>558362</xdr:colOff>
-      <xdr:row>11</xdr:row>
-      <xdr:rowOff>32845</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>4</xdr:col>
-      <xdr:colOff>558362</xdr:colOff>
-      <xdr:row>25</xdr:row>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>17</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>26</xdr:row>
       <xdr:rowOff>0</xdr:rowOff>
-    </xdr:to>
-    <xdr:cxnSp macro="">
-      <xdr:nvCxnSpPr>
-        <xdr:cNvPr id="9" name="直線矢印コネクタ 8">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{8B56B1F7-29CF-4215-AFD4-4B4341237CA9}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvCxnSpPr/>
-      </xdr:nvCxnSpPr>
-      <xdr:spPr>
-        <a:xfrm>
-          <a:off x="3291052" y="1911569"/>
-          <a:ext cx="0" cy="2358259"/>
-        </a:xfrm>
-        <a:prstGeom prst="straightConnector1">
-          <a:avLst/>
-        </a:prstGeom>
-        <a:ln w="38100">
-          <a:solidFill>
-            <a:srgbClr val="FF0000"/>
-          </a:solidFill>
-          <a:tailEnd type="triangle"/>
-        </a:ln>
-      </xdr:spPr>
-      <xdr:style>
-        <a:lnRef idx="1">
-          <a:schemeClr val="accent1"/>
-        </a:lnRef>
-        <a:fillRef idx="0">
-          <a:schemeClr val="accent1"/>
-        </a:fillRef>
-        <a:effectRef idx="0">
-          <a:schemeClr val="accent1"/>
-        </a:effectRef>
-        <a:fontRef idx="minor">
-          <a:schemeClr val="tx1"/>
-        </a:fontRef>
-      </xdr:style>
-    </xdr:cxnSp>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-  <xdr:twoCellAnchor editAs="oneCell">
-    <xdr:from>
-      <xdr:col>1</xdr:col>
-      <xdr:colOff>6569</xdr:colOff>
-      <xdr:row>27</xdr:row>
-      <xdr:rowOff>19707</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>15</xdr:col>
-      <xdr:colOff>500555</xdr:colOff>
-      <xdr:row>38</xdr:row>
-      <xdr:rowOff>157379</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>22</xdr:col>
+      <xdr:colOff>57150</xdr:colOff>
+      <xdr:row>55</xdr:row>
+      <xdr:rowOff>16997</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
-        <xdr:cNvPr id="11" name="図 10">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{3478F6D2-C06D-4D9C-9DCC-E0C7E1AC33CC}"/>
+        <xdr:cNvPr id="9" name="図 8">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{E7920304-7DB1-4730-A439-9E621093422E}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -1676,7 +1764,7 @@
         </xdr:cNvPicPr>
       </xdr:nvPicPr>
       <xdr:blipFill>
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId4" cstate="print">
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId4">
           <a:extLst>
             <a:ext uri="{28A0092B-C50C-407E-A947-70E740481C1C}">
               <a14:useLocalDpi xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" val="0"/>
@@ -1689,8 +1777,8 @@
       </xdr:blipFill>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="689741" y="4631121"/>
-          <a:ext cx="10058400" cy="2016396"/>
+          <a:off x="11658600" y="4457700"/>
+          <a:ext cx="3486150" cy="4989047"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -1702,22 +1790,22 @@
   <xdr:twoCellAnchor>
     <xdr:from>
       <xdr:col>7</xdr:col>
-      <xdr:colOff>617482</xdr:colOff>
+      <xdr:colOff>485774</xdr:colOff>
       <xdr:row>23</xdr:row>
-      <xdr:rowOff>59121</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>13</xdr:col>
-      <xdr:colOff>216775</xdr:colOff>
+      <xdr:rowOff>47626</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>12</xdr:col>
+      <xdr:colOff>430695</xdr:colOff>
       <xdr:row>27</xdr:row>
-      <xdr:rowOff>39414</xdr:rowOff>
+      <xdr:rowOff>66261</xdr:rowOff>
     </xdr:to>
     <xdr:sp macro="" textlink="">
       <xdr:nvSpPr>
-        <xdr:cNvPr id="12" name="吹き出し: 四角形 11">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{3C48985B-30E2-4633-BB2E-28F0A4EC5362}"/>
+        <xdr:cNvPr id="10" name="吹き出し: 四角形 9">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{27A5471B-65C7-40E9-884A-D40DF40F3E20}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -1725,13 +1813,13 @@
       </xdr:nvSpPr>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="5399689" y="3987362"/>
-          <a:ext cx="3698327" cy="663466"/>
+          <a:off x="5297970" y="4048126"/>
+          <a:ext cx="3382203" cy="714374"/>
         </a:xfrm>
         <a:prstGeom prst="wedgeRectCallout">
           <a:avLst>
-            <a:gd name="adj1" fmla="val -39124"/>
-            <a:gd name="adj2" fmla="val 109120"/>
+            <a:gd name="adj1" fmla="val -36321"/>
+            <a:gd name="adj2" fmla="val 102226"/>
           </a:avLst>
         </a:prstGeom>
       </xdr:spPr>
@@ -1764,7 +1852,7 @@
               <a:ea typeface="+mn-ea"/>
               <a:cs typeface="+mn-cs"/>
             </a:rPr>
-            <a:t>NO3.</a:t>
+            <a:t>NO.3</a:t>
           </a:r>
           <a:r>
             <a:rPr lang="ja-JP" altLang="ja-JP" sz="1100">
@@ -1776,10 +1864,10 @@
               <a:ea typeface="+mn-ea"/>
               <a:cs typeface="+mn-cs"/>
             </a:rPr>
-            <a:t>「メールアドレス」のみに情報を入力して検索ボタンを押下したとき、入力した情報が加入者情報テーブルの「メールアドレス」と部分一致したユーザー情報を表示</a:t>
+            <a:t>「氏名」のみに</a:t>
           </a:r>
           <a:r>
-            <a:rPr lang="ja-JP" altLang="en-US" sz="1100">
+            <a:rPr lang="en-US" altLang="ja-JP" sz="1100">
               <a:solidFill>
                 <a:schemeClr val="dk1"/>
               </a:solidFill>
@@ -1788,9 +1876,96 @@
               <a:ea typeface="+mn-ea"/>
               <a:cs typeface="+mn-cs"/>
             </a:rPr>
-            <a:t>される</a:t>
+            <a:t>”</a:t>
           </a:r>
-          <a:endParaRPr kumimoji="1" lang="ja-JP" altLang="en-US" sz="1100"/>
+          <a:r>
+            <a:rPr lang="ja-JP" altLang="ja-JP" sz="1100">
+              <a:solidFill>
+                <a:schemeClr val="dk1"/>
+              </a:solidFill>
+              <a:effectLst/>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:rPr>
+            <a:t>山田</a:t>
+          </a:r>
+          <a:r>
+            <a:rPr lang="en-US" altLang="ja-JP" sz="1100">
+              <a:solidFill>
+                <a:schemeClr val="dk1"/>
+              </a:solidFill>
+              <a:effectLst/>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:rPr>
+            <a:t>”</a:t>
+          </a:r>
+          <a:r>
+            <a:rPr lang="ja-JP" altLang="ja-JP" sz="1100">
+              <a:solidFill>
+                <a:schemeClr val="dk1"/>
+              </a:solidFill>
+              <a:effectLst/>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:rPr>
+            <a:t>と入力して検索ボタンを押下したとき、</a:t>
+          </a:r>
+          <a:r>
+            <a:rPr lang="en-US" altLang="ja-JP" sz="1100">
+              <a:solidFill>
+                <a:schemeClr val="dk1"/>
+              </a:solidFill>
+              <a:effectLst/>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:rPr>
+            <a:t>”</a:t>
+          </a:r>
+          <a:r>
+            <a:rPr lang="ja-JP" altLang="ja-JP" sz="1100">
+              <a:solidFill>
+                <a:schemeClr val="dk1"/>
+              </a:solidFill>
+              <a:effectLst/>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:rPr>
+            <a:t>山田</a:t>
+          </a:r>
+          <a:r>
+            <a:rPr lang="en-US" altLang="ja-JP" sz="1100">
+              <a:solidFill>
+                <a:schemeClr val="dk1"/>
+              </a:solidFill>
+              <a:effectLst/>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:rPr>
+            <a:t>”</a:t>
+          </a:r>
+          <a:r>
+            <a:rPr lang="ja-JP" altLang="ja-JP" sz="1100">
+              <a:solidFill>
+                <a:schemeClr val="dk1"/>
+              </a:solidFill>
+              <a:effectLst/>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:rPr>
+            <a:t>と部分一致した氏名を持つユーザーの情報が表示される</a:t>
+          </a:r>
+          <a:endParaRPr kumimoji="1" lang="ja-JP" altLang="en-US" sz="1100">
+            <a:latin typeface="+mn-ea"/>
+            <a:ea typeface="+mn-ea"/>
+          </a:endParaRPr>
         </a:p>
       </xdr:txBody>
     </xdr:sp>
@@ -1799,22 +1974,22 @@
   <xdr:twoCellAnchor>
     <xdr:from>
       <xdr:col>4</xdr:col>
-      <xdr:colOff>367862</xdr:colOff>
-      <xdr:row>31</xdr:row>
-      <xdr:rowOff>32845</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>5</xdr:col>
-      <xdr:colOff>26276</xdr:colOff>
-      <xdr:row>32</xdr:row>
-      <xdr:rowOff>78827</xdr:rowOff>
+      <xdr:colOff>381000</xdr:colOff>
+      <xdr:row>8</xdr:row>
+      <xdr:rowOff>133350</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>4</xdr:col>
+      <xdr:colOff>676275</xdr:colOff>
+      <xdr:row>10</xdr:row>
+      <xdr:rowOff>19050</xdr:rowOff>
     </xdr:to>
     <xdr:sp macro="" textlink="">
       <xdr:nvSpPr>
-        <xdr:cNvPr id="13" name="正方形/長方形 12">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{307EEC4A-536D-4EA4-8D98-5F3A1F80FD5B}"/>
+        <xdr:cNvPr id="11" name="正方形/長方形 10">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{DF695608-AF92-41C6-88B5-78ED4525EFD7}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -1822,8 +1997,8 @@
       </xdr:nvSpPr>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="3100552" y="5327431"/>
-          <a:ext cx="341586" cy="216775"/>
+          <a:off x="3124200" y="1504950"/>
+          <a:ext cx="295275" cy="228600"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -1867,31 +2042,31 @@
   <xdr:twoCellAnchor>
     <xdr:from>
       <xdr:col>4</xdr:col>
-      <xdr:colOff>512379</xdr:colOff>
-      <xdr:row>32</xdr:row>
-      <xdr:rowOff>144517</xdr:rowOff>
+      <xdr:colOff>517071</xdr:colOff>
+      <xdr:row>10</xdr:row>
+      <xdr:rowOff>104775</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>4</xdr:col>
-      <xdr:colOff>518948</xdr:colOff>
-      <xdr:row>58</xdr:row>
-      <xdr:rowOff>151086</xdr:rowOff>
+      <xdr:colOff>523877</xdr:colOff>
+      <xdr:row>24</xdr:row>
+      <xdr:rowOff>157843</xdr:rowOff>
     </xdr:to>
     <xdr:cxnSp macro="">
       <xdr:nvCxnSpPr>
-        <xdr:cNvPr id="14" name="直線矢印コネクタ 13">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{8C7E0BFB-C59F-4B70-8459-2D26A70773A0}"/>
+        <xdr:cNvPr id="13" name="直線矢印コネクタ 12">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{615910B6-6514-41F9-9875-7C4CE0402CE3}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
         <xdr:cNvCxnSpPr/>
       </xdr:nvCxnSpPr>
       <xdr:spPr>
-        <a:xfrm>
-          <a:off x="3245069" y="5609896"/>
-          <a:ext cx="6569" cy="4447190"/>
+        <a:xfrm flipH="1">
+          <a:off x="3260271" y="1846489"/>
+          <a:ext cx="6806" cy="2491468"/>
         </a:xfrm>
         <a:prstGeom prst="straightConnector1">
           <a:avLst/>
@@ -1920,25 +2095,230 @@
     </xdr:cxnSp>
     <xdr:clientData/>
   </xdr:twoCellAnchor>
+</xdr:wsDr>
+</file>
+
+<file path=xl/drawings/drawing5.xml><?xml version="1.0" encoding="utf-8"?>
+<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
   <xdr:twoCellAnchor editAs="oneCell">
     <xdr:from>
-      <xdr:col>0</xdr:col>
-      <xdr:colOff>683172</xdr:colOff>
-      <xdr:row>60</xdr:row>
+      <xdr:col>1</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>3</xdr:row>
       <xdr:rowOff>0</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>15</xdr:col>
-      <xdr:colOff>493986</xdr:colOff>
-      <xdr:row>69</xdr:row>
-      <xdr:rowOff>78337</xdr:rowOff>
+      <xdr:colOff>457200</xdr:colOff>
+      <xdr:row>11</xdr:row>
+      <xdr:rowOff>102374</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
-        <xdr:cNvPr id="18" name="図 17">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{362A9CE4-DFE2-4DF9-88B6-158A5474DB21}"/>
+        <xdr:cNvPr id="3" name="図 2">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{0331387E-88CE-472A-8881-4CD806A3FA3D}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId1" cstate="print">
+          <a:extLst>
+            <a:ext uri="{28A0092B-C50C-407E-A947-70E740481C1C}">
+              <a14:useLocalDpi xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" val="0"/>
+            </a:ext>
+          </a:extLst>
+        </a:blip>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="685800" y="514350"/>
+          <a:ext cx="10058400" cy="1473974"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>17</xdr:col>
+      <xdr:colOff>1</xdr:colOff>
+      <xdr:row>3</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>22</xdr:col>
+      <xdr:colOff>452658</xdr:colOff>
+      <xdr:row>24</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="5" name="図 4">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{D53D42BC-D80F-4967-8227-822ADD165F6A}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId2">
+          <a:extLst>
+            <a:ext uri="{28A0092B-C50C-407E-A947-70E740481C1C}">
+              <a14:useLocalDpi xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" val="0"/>
+            </a:ext>
+          </a:extLst>
+        </a:blip>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="11658601" y="514350"/>
+          <a:ext cx="3881657" cy="3600450"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>1</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>27</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>15</xdr:col>
+      <xdr:colOff>457200</xdr:colOff>
+      <xdr:row>35</xdr:row>
+      <xdr:rowOff>169194</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="7" name="図 6">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{D15F78EC-A612-4060-8841-1FB5B703628C}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId3" cstate="print">
+          <a:extLst>
+            <a:ext uri="{28A0092B-C50C-407E-A947-70E740481C1C}">
+              <a14:useLocalDpi xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" val="0"/>
+            </a:ext>
+          </a:extLst>
+        </a:blip>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="685800" y="4629150"/>
+          <a:ext cx="10058400" cy="1540794"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>17</xdr:col>
+      <xdr:colOff>1</xdr:colOff>
+      <xdr:row>26</xdr:row>
+      <xdr:rowOff>171449</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>22</xdr:col>
+      <xdr:colOff>523875</xdr:colOff>
+      <xdr:row>59</xdr:row>
+      <xdr:rowOff>170298</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="9" name="図 8">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{3AF8DB0E-45D8-40F0-AFE5-9BD1A9EE29D7}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId4">
+          <a:extLst>
+            <a:ext uri="{28A0092B-C50C-407E-A947-70E740481C1C}">
+              <a14:useLocalDpi xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" val="0"/>
+            </a:ext>
+          </a:extLst>
+        </a:blip>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="11658601" y="4629149"/>
+          <a:ext cx="3952874" cy="5656699"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>1</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>61</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>15</xdr:col>
+      <xdr:colOff>457200</xdr:colOff>
+      <xdr:row>70</xdr:row>
+      <xdr:rowOff>52772</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="11" name="図 10">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{BC555D75-4D62-4A25-AFE0-0AD32F937B40}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -1960,8 +2340,8 @@
       </xdr:blipFill>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="683172" y="10247586"/>
-          <a:ext cx="10058400" cy="1615475"/>
+          <a:off x="685800" y="10458450"/>
+          <a:ext cx="10058400" cy="1595822"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -1972,23 +2352,23 @@
   </xdr:twoCellAnchor>
   <xdr:twoCellAnchor>
     <xdr:from>
-      <xdr:col>6</xdr:col>
-      <xdr:colOff>354725</xdr:colOff>
-      <xdr:row>57</xdr:row>
-      <xdr:rowOff>151086</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>10</xdr:col>
-      <xdr:colOff>302173</xdr:colOff>
-      <xdr:row>60</xdr:row>
-      <xdr:rowOff>157656</xdr:rowOff>
+      <xdr:col>4</xdr:col>
+      <xdr:colOff>390525</xdr:colOff>
+      <xdr:row>9</xdr:row>
+      <xdr:rowOff>66675</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>5</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>10</xdr:row>
+      <xdr:rowOff>123825</xdr:rowOff>
     </xdr:to>
     <xdr:sp macro="" textlink="">
       <xdr:nvSpPr>
-        <xdr:cNvPr id="20" name="吹き出し: 四角形 19">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{DBAE1ADA-205F-4086-8B16-75A10CACFAA5}"/>
+        <xdr:cNvPr id="15" name="正方形/長方形 14">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{4B3C217B-5620-493C-8B54-6618C50F2974}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -1996,121 +2376,164 @@
       </xdr:nvSpPr>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="4453759" y="9886293"/>
-          <a:ext cx="2680138" cy="518949"/>
-        </a:xfrm>
-        <a:prstGeom prst="wedgeRectCallout">
-          <a:avLst>
-            <a:gd name="adj1" fmla="val -32990"/>
-            <a:gd name="adj2" fmla="val 106764"/>
-          </a:avLst>
-        </a:prstGeom>
+          <a:off x="3133725" y="1609725"/>
+          <a:ext cx="295275" cy="228600"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:noFill/>
+        <a:ln w="38100" cap="flat" cmpd="sng" algn="ctr">
+          <a:solidFill>
+            <a:srgbClr val="FF0000"/>
+          </a:solidFill>
+          <a:prstDash val="solid"/>
+          <a:round/>
+          <a:headEnd type="none" w="med" len="med"/>
+          <a:tailEnd type="none" w="med" len="med"/>
+        </a:ln>
       </xdr:spPr>
       <xdr:style>
-        <a:lnRef idx="2">
-          <a:schemeClr val="accent1"/>
+        <a:lnRef idx="0">
+          <a:scrgbClr r="0" g="0" b="0"/>
         </a:lnRef>
-        <a:fillRef idx="1">
-          <a:schemeClr val="lt1"/>
+        <a:fillRef idx="0">
+          <a:scrgbClr r="0" g="0" b="0"/>
         </a:fillRef>
         <a:effectRef idx="0">
-          <a:schemeClr val="accent1"/>
+          <a:scrgbClr r="0" g="0" b="0"/>
         </a:effectRef>
         <a:fontRef idx="minor">
-          <a:schemeClr val="dk1"/>
+          <a:schemeClr val="accent2"/>
         </a:fontRef>
       </xdr:style>
       <xdr:txBody>
         <a:bodyPr vertOverflow="clip" horzOverflow="clip" rtlCol="0" anchor="t"/>
         <a:lstStyle/>
         <a:p>
-          <a:pPr marL="0" marR="0" lvl="0" indent="0" algn="l" defTabSz="914400" eaLnBrk="1" fontAlgn="auto" latinLnBrk="0" hangingPunct="1">
-            <a:lnSpc>
-              <a:spcPct val="100000"/>
-            </a:lnSpc>
-            <a:spcBef>
-              <a:spcPts val="0"/>
-            </a:spcBef>
-            <a:spcAft>
-              <a:spcPts val="0"/>
-            </a:spcAft>
-            <a:buClrTx/>
-            <a:buSzTx/>
-            <a:buFontTx/>
-            <a:buNone/>
-            <a:tabLst/>
-            <a:defRPr/>
-          </a:pPr>
-          <a:r>
-            <a:rPr lang="en-US" altLang="ja-JP" sz="1100">
-              <a:solidFill>
-                <a:schemeClr val="dk1"/>
-              </a:solidFill>
-              <a:effectLst/>
-              <a:latin typeface="+mn-lt"/>
-              <a:ea typeface="+mn-ea"/>
-              <a:cs typeface="+mn-cs"/>
-            </a:rPr>
-            <a:t>NO4.</a:t>
-          </a:r>
-          <a:r>
-            <a:rPr lang="ja-JP" altLang="ja-JP" sz="1100">
-              <a:solidFill>
-                <a:schemeClr val="dk1"/>
-              </a:solidFill>
-              <a:effectLst/>
-              <a:latin typeface="+mn-lt"/>
-              <a:ea typeface="+mn-ea"/>
-              <a:cs typeface="+mn-cs"/>
-            </a:rPr>
-            <a:t>戻るボタンを押下して</a:t>
-          </a:r>
-          <a:r>
-            <a:rPr lang="ja-JP" altLang="en-US" sz="1100">
-              <a:solidFill>
-                <a:schemeClr val="dk1"/>
-              </a:solidFill>
-              <a:effectLst/>
-              <a:latin typeface="+mn-lt"/>
-              <a:ea typeface="+mn-ea"/>
-              <a:cs typeface="+mn-cs"/>
-            </a:rPr>
-            <a:t>加入者情報</a:t>
-          </a:r>
-          <a:r>
-            <a:rPr lang="ja-JP" altLang="ja-JP" sz="1100">
-              <a:solidFill>
-                <a:schemeClr val="dk1"/>
-              </a:solidFill>
-              <a:effectLst/>
-              <a:latin typeface="+mn-lt"/>
-              <a:ea typeface="+mn-ea"/>
-              <a:cs typeface="+mn-cs"/>
-            </a:rPr>
-            <a:t>検索画面に</a:t>
-          </a:r>
-          <a:r>
-            <a:rPr lang="ja-JP" altLang="en-US" sz="1100">
-              <a:solidFill>
-                <a:schemeClr val="dk1"/>
-              </a:solidFill>
-              <a:effectLst/>
-              <a:latin typeface="+mn-lt"/>
-              <a:ea typeface="+mn-ea"/>
-              <a:cs typeface="+mn-cs"/>
-            </a:rPr>
-            <a:t>もどれる</a:t>
-          </a:r>
-          <a:endParaRPr lang="ja-JP" altLang="ja-JP" sz="1100">
-            <a:solidFill>
-              <a:schemeClr val="dk1"/>
-            </a:solidFill>
-            <a:effectLst/>
-            <a:latin typeface="+mn-lt"/>
-            <a:ea typeface="+mn-ea"/>
-            <a:cs typeface="+mn-cs"/>
-          </a:endParaRPr>
+          <a:pPr algn="l"/>
+          <a:endParaRPr kumimoji="1" lang="ja-JP" altLang="en-US" sz="1100"/>
         </a:p>
+      </xdr:txBody>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>4</xdr:col>
+      <xdr:colOff>485775</xdr:colOff>
+      <xdr:row>11</xdr:row>
+      <xdr:rowOff>19050</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>4</xdr:col>
+      <xdr:colOff>504825</xdr:colOff>
+      <xdr:row>25</xdr:row>
+      <xdr:rowOff>123825</xdr:rowOff>
+    </xdr:to>
+    <xdr:cxnSp macro="">
+      <xdr:nvCxnSpPr>
+        <xdr:cNvPr id="17" name="直線矢印コネクタ 16">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{4A3F4E6B-314D-47F4-BD2F-0BBEA2A39230}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvCxnSpPr/>
+      </xdr:nvCxnSpPr>
+      <xdr:spPr>
+        <a:xfrm flipH="1">
+          <a:off x="3228975" y="1905000"/>
+          <a:ext cx="19050" cy="2505075"/>
+        </a:xfrm>
+        <a:prstGeom prst="straightConnector1">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:ln w="38100">
+          <a:solidFill>
+            <a:srgbClr val="FF0000"/>
+          </a:solidFill>
+          <a:tailEnd type="triangle"/>
+        </a:ln>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="1">
+          <a:schemeClr val="accent1"/>
+        </a:lnRef>
+        <a:fillRef idx="0">
+          <a:schemeClr val="accent1"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:schemeClr val="accent1"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="tx1"/>
+        </a:fontRef>
+      </xdr:style>
+    </xdr:cxnSp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>4</xdr:col>
+      <xdr:colOff>390525</xdr:colOff>
+      <xdr:row>31</xdr:row>
+      <xdr:rowOff>28575</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>5</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>32</xdr:row>
+      <xdr:rowOff>85725</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="18" name="正方形/長方形 17">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{3B0D2B3B-6A44-4430-BD1F-35A060DAAA47}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvSpPr/>
+      </xdr:nvSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="3133725" y="5343525"/>
+          <a:ext cx="295275" cy="228600"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:noFill/>
+        <a:ln w="38100" cap="flat" cmpd="sng" algn="ctr">
+          <a:solidFill>
+            <a:srgbClr val="FF0000"/>
+          </a:solidFill>
+          <a:prstDash val="solid"/>
+          <a:round/>
+          <a:headEnd type="none" w="med" len="med"/>
+          <a:tailEnd type="none" w="med" len="med"/>
+        </a:ln>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="0">
+          <a:scrgbClr r="0" g="0" b="0"/>
+        </a:lnRef>
+        <a:fillRef idx="0">
+          <a:scrgbClr r="0" g="0" b="0"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:scrgbClr r="0" g="0" b="0"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="accent2"/>
+        </a:fontRef>
+      </xdr:style>
+      <xdr:txBody>
+        <a:bodyPr vertOverflow="clip" horzOverflow="clip" rtlCol="0" anchor="t"/>
+        <a:lstStyle/>
         <a:p>
           <a:pPr algn="l"/>
           <a:endParaRPr kumimoji="1" lang="ja-JP" altLang="en-US" sz="1100"/>
@@ -2119,230 +2542,81 @@
     </xdr:sp>
     <xdr:clientData/>
   </xdr:twoCellAnchor>
-</xdr:wsDr>
-</file>
-
-<file path=xl/drawings/drawing4.xml><?xml version="1.0" encoding="utf-8"?>
-<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-  <xdr:twoCellAnchor editAs="oneCell">
-    <xdr:from>
-      <xdr:col>1</xdr:col>
-      <xdr:colOff>0</xdr:colOff>
-      <xdr:row>3</xdr:row>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>4</xdr:col>
+      <xdr:colOff>542925</xdr:colOff>
+      <xdr:row>33</xdr:row>
       <xdr:rowOff>0</xdr:rowOff>
     </xdr:from>
     <xdr:to>
-      <xdr:col>15</xdr:col>
-      <xdr:colOff>457200</xdr:colOff>
-      <xdr:row>11</xdr:row>
-      <xdr:rowOff>102374</xdr:rowOff>
-    </xdr:to>
-    <xdr:pic>
-      <xdr:nvPicPr>
-        <xdr:cNvPr id="3" name="図 2">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{3FB681B9-4082-49B7-BA0E-76B627168F5D}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvPicPr>
-          <a:picLocks noChangeAspect="1"/>
-        </xdr:cNvPicPr>
-      </xdr:nvPicPr>
-      <xdr:blipFill>
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId1" cstate="print">
-          <a:extLst>
-            <a:ext uri="{28A0092B-C50C-407E-A947-70E740481C1C}">
-              <a14:useLocalDpi xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" val="0"/>
-            </a:ext>
-          </a:extLst>
-        </a:blip>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </xdr:blipFill>
-      <xdr:spPr>
-        <a:xfrm>
-          <a:off x="685800" y="514350"/>
-          <a:ext cx="10058400" cy="1473974"/>
-        </a:xfrm>
-        <a:prstGeom prst="rect">
+      <xdr:col>4</xdr:col>
+      <xdr:colOff>552450</xdr:colOff>
+      <xdr:row>60</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:to>
+    <xdr:cxnSp macro="">
+      <xdr:nvCxnSpPr>
+        <xdr:cNvPr id="19" name="直線矢印コネクタ 18">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{2EE743A1-5D21-49F6-B0E9-F1E755F35648}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvCxnSpPr/>
+      </xdr:nvCxnSpPr>
+      <xdr:spPr>
+        <a:xfrm flipH="1">
+          <a:off x="3286125" y="5657850"/>
+          <a:ext cx="9525" cy="4629150"/>
+        </a:xfrm>
+        <a:prstGeom prst="straightConnector1">
           <a:avLst/>
         </a:prstGeom>
-      </xdr:spPr>
-    </xdr:pic>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-  <xdr:twoCellAnchor editAs="oneCell">
-    <xdr:from>
-      <xdr:col>17</xdr:col>
-      <xdr:colOff>6569</xdr:colOff>
-      <xdr:row>2</xdr:row>
-      <xdr:rowOff>144517</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>22</xdr:col>
-      <xdr:colOff>157654</xdr:colOff>
-      <xdr:row>22</xdr:row>
-      <xdr:rowOff>34410</xdr:rowOff>
-    </xdr:to>
-    <xdr:pic>
-      <xdr:nvPicPr>
-        <xdr:cNvPr id="5" name="図 4">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{381A5ABC-B53A-40DA-BD21-46EADC4CA750}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvPicPr>
-          <a:picLocks noChangeAspect="1"/>
-        </xdr:cNvPicPr>
-      </xdr:nvPicPr>
-      <xdr:blipFill>
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId2">
-          <a:extLst>
-            <a:ext uri="{28A0092B-C50C-407E-A947-70E740481C1C}">
-              <a14:useLocalDpi xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" val="0"/>
-            </a:ext>
-          </a:extLst>
-        </a:blip>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </xdr:blipFill>
-      <xdr:spPr>
-        <a:xfrm>
-          <a:off x="11620500" y="486103"/>
-          <a:ext cx="3566947" cy="3305755"/>
-        </a:xfrm>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-      </xdr:spPr>
-    </xdr:pic>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-  <xdr:twoCellAnchor editAs="oneCell">
-    <xdr:from>
-      <xdr:col>0</xdr:col>
-      <xdr:colOff>683172</xdr:colOff>
-      <xdr:row>26</xdr:row>
-      <xdr:rowOff>6569</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>15</xdr:col>
-      <xdr:colOff>493986</xdr:colOff>
-      <xdr:row>36</xdr:row>
-      <xdr:rowOff>587</xdr:rowOff>
-    </xdr:to>
-    <xdr:pic>
-      <xdr:nvPicPr>
-        <xdr:cNvPr id="7" name="図 6">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{806FDD9E-5007-4DCB-82EE-554046F924ED}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvPicPr>
-          <a:picLocks noChangeAspect="1"/>
-        </xdr:cNvPicPr>
-      </xdr:nvPicPr>
-      <xdr:blipFill>
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId3" cstate="print">
-          <a:extLst>
-            <a:ext uri="{28A0092B-C50C-407E-A947-70E740481C1C}">
-              <a14:useLocalDpi xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" val="0"/>
-            </a:ext>
-          </a:extLst>
-        </a:blip>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </xdr:blipFill>
-      <xdr:spPr>
-        <a:xfrm>
-          <a:off x="683172" y="4447190"/>
-          <a:ext cx="10058400" cy="1701949"/>
-        </a:xfrm>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-      </xdr:spPr>
-    </xdr:pic>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-  <xdr:twoCellAnchor editAs="oneCell">
-    <xdr:from>
-      <xdr:col>17</xdr:col>
-      <xdr:colOff>0</xdr:colOff>
-      <xdr:row>26</xdr:row>
-      <xdr:rowOff>0</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>22</xdr:col>
-      <xdr:colOff>57150</xdr:colOff>
-      <xdr:row>55</xdr:row>
-      <xdr:rowOff>16997</xdr:rowOff>
-    </xdr:to>
-    <xdr:pic>
-      <xdr:nvPicPr>
-        <xdr:cNvPr id="9" name="図 8">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{E7920304-7DB1-4730-A439-9E621093422E}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvPicPr>
-          <a:picLocks noChangeAspect="1"/>
-        </xdr:cNvPicPr>
-      </xdr:nvPicPr>
-      <xdr:blipFill>
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId4">
-          <a:extLst>
-            <a:ext uri="{28A0092B-C50C-407E-A947-70E740481C1C}">
-              <a14:useLocalDpi xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" val="0"/>
-            </a:ext>
-          </a:extLst>
-        </a:blip>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </xdr:blipFill>
-      <xdr:spPr>
-        <a:xfrm>
-          <a:off x="11658600" y="4457700"/>
-          <a:ext cx="3486150" cy="4989047"/>
-        </a:xfrm>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-      </xdr:spPr>
-    </xdr:pic>
+        <a:ln w="38100">
+          <a:solidFill>
+            <a:srgbClr val="FF0000"/>
+          </a:solidFill>
+          <a:tailEnd type="triangle"/>
+        </a:ln>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="1">
+          <a:schemeClr val="accent1"/>
+        </a:lnRef>
+        <a:fillRef idx="0">
+          <a:schemeClr val="accent1"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:schemeClr val="accent1"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="tx1"/>
+        </a:fontRef>
+      </xdr:style>
+    </xdr:cxnSp>
     <xdr:clientData/>
   </xdr:twoCellAnchor>
   <xdr:twoCellAnchor>
     <xdr:from>
       <xdr:col>7</xdr:col>
-      <xdr:colOff>485774</xdr:colOff>
-      <xdr:row>23</xdr:row>
-      <xdr:rowOff>47626</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>12</xdr:col>
-      <xdr:colOff>430695</xdr:colOff>
-      <xdr:row>27</xdr:row>
-      <xdr:rowOff>66261</xdr:rowOff>
+      <xdr:colOff>127395</xdr:colOff>
+      <xdr:row>24</xdr:row>
+      <xdr:rowOff>82155</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>11</xdr:col>
+      <xdr:colOff>458390</xdr:colOff>
+      <xdr:row>29</xdr:row>
+      <xdr:rowOff>107158</xdr:rowOff>
     </xdr:to>
     <xdr:sp macro="" textlink="">
       <xdr:nvSpPr>
-        <xdr:cNvPr id="10" name="吹き出し: 四角形 9">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{27A5471B-65C7-40E9-884A-D40DF40F3E20}"/>
+        <xdr:cNvPr id="22" name="吹き出し: 四角形 21">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{57903372-E62F-40FA-9DA8-75259CBA1D0B}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -2350,13 +2624,13 @@
       </xdr:nvSpPr>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="5297970" y="4048126"/>
-          <a:ext cx="3382203" cy="714374"/>
+          <a:off x="4919661" y="4225530"/>
+          <a:ext cx="3069432" cy="888206"/>
         </a:xfrm>
         <a:prstGeom prst="wedgeRectCallout">
           <a:avLst>
-            <a:gd name="adj1" fmla="val -36321"/>
-            <a:gd name="adj2" fmla="val 102226"/>
+            <a:gd name="adj1" fmla="val -34798"/>
+            <a:gd name="adj2" fmla="val 73022"/>
           </a:avLst>
         </a:prstGeom>
       </xdr:spPr>
@@ -2389,1062 +2663,8 @@
               <a:ea typeface="+mn-ea"/>
               <a:cs typeface="+mn-cs"/>
             </a:rPr>
-            <a:t>NO.5</a:t>
+            <a:t>NO.4</a:t>
           </a:r>
-          <a:r>
-            <a:rPr lang="ja-JP" altLang="ja-JP" sz="1100">
-              <a:solidFill>
-                <a:schemeClr val="dk1"/>
-              </a:solidFill>
-              <a:effectLst/>
-              <a:latin typeface="+mn-ea"/>
-              <a:ea typeface="+mn-ea"/>
-              <a:cs typeface="+mn-cs"/>
-            </a:rPr>
-            <a:t>「氏名」のみに情報を入力して検索ボタンを押下したとき、入力した情報が加入者情報テーブルの「氏名」と部分一致したユーザー情報を表示</a:t>
-          </a:r>
-          <a:r>
-            <a:rPr lang="ja-JP" altLang="en-US" sz="1100">
-              <a:solidFill>
-                <a:schemeClr val="dk1"/>
-              </a:solidFill>
-              <a:effectLst/>
-              <a:latin typeface="+mn-ea"/>
-              <a:ea typeface="+mn-ea"/>
-              <a:cs typeface="+mn-cs"/>
-            </a:rPr>
-            <a:t>される</a:t>
-          </a:r>
-          <a:endParaRPr kumimoji="1" lang="ja-JP" altLang="en-US" sz="1100">
-            <a:latin typeface="+mn-ea"/>
-            <a:ea typeface="+mn-ea"/>
-          </a:endParaRPr>
-        </a:p>
-      </xdr:txBody>
-    </xdr:sp>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-  <xdr:twoCellAnchor>
-    <xdr:from>
-      <xdr:col>4</xdr:col>
-      <xdr:colOff>381000</xdr:colOff>
-      <xdr:row>8</xdr:row>
-      <xdr:rowOff>133350</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>4</xdr:col>
-      <xdr:colOff>676275</xdr:colOff>
-      <xdr:row>10</xdr:row>
-      <xdr:rowOff>19050</xdr:rowOff>
-    </xdr:to>
-    <xdr:sp macro="" textlink="">
-      <xdr:nvSpPr>
-        <xdr:cNvPr id="11" name="正方形/長方形 10">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{DF695608-AF92-41C6-88B5-78ED4525EFD7}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvSpPr/>
-      </xdr:nvSpPr>
-      <xdr:spPr>
-        <a:xfrm>
-          <a:off x="3124200" y="1504950"/>
-          <a:ext cx="295275" cy="228600"/>
-        </a:xfrm>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-        <a:noFill/>
-        <a:ln w="38100" cap="flat" cmpd="sng" algn="ctr">
-          <a:solidFill>
-            <a:srgbClr val="FF0000"/>
-          </a:solidFill>
-          <a:prstDash val="solid"/>
-          <a:round/>
-          <a:headEnd type="none" w="med" len="med"/>
-          <a:tailEnd type="none" w="med" len="med"/>
-        </a:ln>
-      </xdr:spPr>
-      <xdr:style>
-        <a:lnRef idx="0">
-          <a:scrgbClr r="0" g="0" b="0"/>
-        </a:lnRef>
-        <a:fillRef idx="0">
-          <a:scrgbClr r="0" g="0" b="0"/>
-        </a:fillRef>
-        <a:effectRef idx="0">
-          <a:scrgbClr r="0" g="0" b="0"/>
-        </a:effectRef>
-        <a:fontRef idx="minor">
-          <a:schemeClr val="accent2"/>
-        </a:fontRef>
-      </xdr:style>
-      <xdr:txBody>
-        <a:bodyPr vertOverflow="clip" horzOverflow="clip" rtlCol="0" anchor="t"/>
-        <a:lstStyle/>
-        <a:p>
-          <a:pPr algn="l"/>
-          <a:endParaRPr kumimoji="1" lang="ja-JP" altLang="en-US" sz="1100"/>
-        </a:p>
-      </xdr:txBody>
-    </xdr:sp>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-  <xdr:twoCellAnchor>
-    <xdr:from>
-      <xdr:col>4</xdr:col>
-      <xdr:colOff>517071</xdr:colOff>
-      <xdr:row>10</xdr:row>
-      <xdr:rowOff>104775</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>4</xdr:col>
-      <xdr:colOff>523877</xdr:colOff>
-      <xdr:row>24</xdr:row>
-      <xdr:rowOff>157843</xdr:rowOff>
-    </xdr:to>
-    <xdr:cxnSp macro="">
-      <xdr:nvCxnSpPr>
-        <xdr:cNvPr id="13" name="直線矢印コネクタ 12">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{615910B6-6514-41F9-9875-7C4CE0402CE3}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvCxnSpPr/>
-      </xdr:nvCxnSpPr>
-      <xdr:spPr>
-        <a:xfrm flipH="1">
-          <a:off x="3260271" y="1846489"/>
-          <a:ext cx="6806" cy="2491468"/>
-        </a:xfrm>
-        <a:prstGeom prst="straightConnector1">
-          <a:avLst/>
-        </a:prstGeom>
-        <a:ln w="38100">
-          <a:solidFill>
-            <a:srgbClr val="FF0000"/>
-          </a:solidFill>
-          <a:tailEnd type="triangle"/>
-        </a:ln>
-      </xdr:spPr>
-      <xdr:style>
-        <a:lnRef idx="1">
-          <a:schemeClr val="accent1"/>
-        </a:lnRef>
-        <a:fillRef idx="0">
-          <a:schemeClr val="accent1"/>
-        </a:fillRef>
-        <a:effectRef idx="0">
-          <a:schemeClr val="accent1"/>
-        </a:effectRef>
-        <a:fontRef idx="minor">
-          <a:schemeClr val="tx1"/>
-        </a:fontRef>
-      </xdr:style>
-    </xdr:cxnSp>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-  <xdr:twoCellAnchor editAs="oneCell">
-    <xdr:from>
-      <xdr:col>1</xdr:col>
-      <xdr:colOff>0</xdr:colOff>
-      <xdr:row>57</xdr:row>
-      <xdr:rowOff>0</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>15</xdr:col>
-      <xdr:colOff>434009</xdr:colOff>
-      <xdr:row>66</xdr:row>
-      <xdr:rowOff>160119</xdr:rowOff>
-    </xdr:to>
-    <xdr:pic>
-      <xdr:nvPicPr>
-        <xdr:cNvPr id="19" name="図 18">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{27AC6202-6658-4640-A736-5A5BECEA24F3}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvPicPr>
-          <a:picLocks noChangeAspect="1"/>
-        </xdr:cNvPicPr>
-      </xdr:nvPicPr>
-      <xdr:blipFill>
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId5" cstate="print">
-          <a:extLst>
-            <a:ext uri="{28A0092B-C50C-407E-A947-70E740481C1C}">
-              <a14:useLocalDpi xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" val="0"/>
-            </a:ext>
-          </a:extLst>
-        </a:blip>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </xdr:blipFill>
-      <xdr:spPr>
-        <a:xfrm>
-          <a:off x="687457" y="9914283"/>
-          <a:ext cx="10058400" cy="1725532"/>
-        </a:xfrm>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-      </xdr:spPr>
-    </xdr:pic>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-  <xdr:twoCellAnchor>
-    <xdr:from>
-      <xdr:col>4</xdr:col>
-      <xdr:colOff>381000</xdr:colOff>
-      <xdr:row>29</xdr:row>
-      <xdr:rowOff>165652</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>4</xdr:col>
-      <xdr:colOff>676275</xdr:colOff>
-      <xdr:row>31</xdr:row>
-      <xdr:rowOff>51353</xdr:rowOff>
-    </xdr:to>
-    <xdr:sp macro="" textlink="">
-      <xdr:nvSpPr>
-        <xdr:cNvPr id="20" name="正方形/長方形 19">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{43B251FD-076B-4D56-89F3-F85E367A226F}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvSpPr/>
-      </xdr:nvSpPr>
-      <xdr:spPr>
-        <a:xfrm>
-          <a:off x="3130826" y="5209761"/>
-          <a:ext cx="295275" cy="233570"/>
-        </a:xfrm>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-        <a:noFill/>
-        <a:ln w="38100" cap="flat" cmpd="sng" algn="ctr">
-          <a:solidFill>
-            <a:srgbClr val="FF0000"/>
-          </a:solidFill>
-          <a:prstDash val="solid"/>
-          <a:round/>
-          <a:headEnd type="none" w="med" len="med"/>
-          <a:tailEnd type="none" w="med" len="med"/>
-        </a:ln>
-      </xdr:spPr>
-      <xdr:style>
-        <a:lnRef idx="0">
-          <a:scrgbClr r="0" g="0" b="0"/>
-        </a:lnRef>
-        <a:fillRef idx="0">
-          <a:scrgbClr r="0" g="0" b="0"/>
-        </a:fillRef>
-        <a:effectRef idx="0">
-          <a:scrgbClr r="0" g="0" b="0"/>
-        </a:effectRef>
-        <a:fontRef idx="minor">
-          <a:schemeClr val="accent2"/>
-        </a:fontRef>
-      </xdr:style>
-      <xdr:txBody>
-        <a:bodyPr vertOverflow="clip" horzOverflow="clip" rtlCol="0" anchor="t"/>
-        <a:lstStyle/>
-        <a:p>
-          <a:pPr algn="l"/>
-          <a:endParaRPr kumimoji="1" lang="ja-JP" altLang="en-US" sz="1100"/>
-        </a:p>
-      </xdr:txBody>
-    </xdr:sp>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-  <xdr:twoCellAnchor>
-    <xdr:from>
-      <xdr:col>4</xdr:col>
-      <xdr:colOff>586589</xdr:colOff>
-      <xdr:row>31</xdr:row>
-      <xdr:rowOff>149087</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>4</xdr:col>
-      <xdr:colOff>588065</xdr:colOff>
-      <xdr:row>55</xdr:row>
-      <xdr:rowOff>149087</xdr:rowOff>
-    </xdr:to>
-    <xdr:cxnSp macro="">
-      <xdr:nvCxnSpPr>
-        <xdr:cNvPr id="21" name="直線矢印コネクタ 20">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{C6B4C09E-0786-4AC9-9292-6128FB27699A}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvCxnSpPr/>
-      </xdr:nvCxnSpPr>
-      <xdr:spPr>
-        <a:xfrm>
-          <a:off x="3336415" y="5541065"/>
-          <a:ext cx="1476" cy="4174435"/>
-        </a:xfrm>
-        <a:prstGeom prst="straightConnector1">
-          <a:avLst/>
-        </a:prstGeom>
-        <a:ln w="38100">
-          <a:solidFill>
-            <a:srgbClr val="FF0000"/>
-          </a:solidFill>
-          <a:tailEnd type="triangle"/>
-        </a:ln>
-      </xdr:spPr>
-      <xdr:style>
-        <a:lnRef idx="1">
-          <a:schemeClr val="accent1"/>
-        </a:lnRef>
-        <a:fillRef idx="0">
-          <a:schemeClr val="accent1"/>
-        </a:fillRef>
-        <a:effectRef idx="0">
-          <a:schemeClr val="accent1"/>
-        </a:effectRef>
-        <a:fontRef idx="minor">
-          <a:schemeClr val="tx1"/>
-        </a:fontRef>
-      </xdr:style>
-    </xdr:cxnSp>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-  <xdr:twoCellAnchor>
-    <xdr:from>
-      <xdr:col>6</xdr:col>
-      <xdr:colOff>629478</xdr:colOff>
-      <xdr:row>55</xdr:row>
-      <xdr:rowOff>82825</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>10</xdr:col>
-      <xdr:colOff>610914</xdr:colOff>
-      <xdr:row>58</xdr:row>
-      <xdr:rowOff>107674</xdr:rowOff>
-    </xdr:to>
-    <xdr:sp macro="" textlink="">
-      <xdr:nvSpPr>
-        <xdr:cNvPr id="27" name="吹き出し: 四角形 26">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{1B315BDB-F8D7-415C-9A68-D7A504EBF43B}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvSpPr/>
-      </xdr:nvSpPr>
-      <xdr:spPr>
-        <a:xfrm>
-          <a:off x="4728512" y="9476446"/>
-          <a:ext cx="2714126" cy="537228"/>
-        </a:xfrm>
-        <a:prstGeom prst="wedgeRectCallout">
-          <a:avLst>
-            <a:gd name="adj1" fmla="val -36321"/>
-            <a:gd name="adj2" fmla="val 102226"/>
-          </a:avLst>
-        </a:prstGeom>
-      </xdr:spPr>
-      <xdr:style>
-        <a:lnRef idx="2">
-          <a:schemeClr val="accent1"/>
-        </a:lnRef>
-        <a:fillRef idx="1">
-          <a:schemeClr val="lt1"/>
-        </a:fillRef>
-        <a:effectRef idx="0">
-          <a:schemeClr val="accent1"/>
-        </a:effectRef>
-        <a:fontRef idx="minor">
-          <a:schemeClr val="dk1"/>
-        </a:fontRef>
-      </xdr:style>
-      <xdr:txBody>
-        <a:bodyPr vertOverflow="clip" horzOverflow="clip" rtlCol="0" anchor="t"/>
-        <a:lstStyle/>
-        <a:p>
-          <a:pPr marL="0" marR="0" lvl="0" indent="0" algn="l" defTabSz="914400" eaLnBrk="1" fontAlgn="auto" latinLnBrk="0" hangingPunct="1">
-            <a:lnSpc>
-              <a:spcPct val="100000"/>
-            </a:lnSpc>
-            <a:spcBef>
-              <a:spcPts val="0"/>
-            </a:spcBef>
-            <a:spcAft>
-              <a:spcPts val="0"/>
-            </a:spcAft>
-            <a:buClrTx/>
-            <a:buSzTx/>
-            <a:buFontTx/>
-            <a:buNone/>
-            <a:tabLst/>
-            <a:defRPr/>
-          </a:pPr>
-          <a:r>
-            <a:rPr lang="en-US" altLang="ja-JP" sz="1100">
-              <a:solidFill>
-                <a:schemeClr val="dk1"/>
-              </a:solidFill>
-              <a:effectLst/>
-              <a:latin typeface="Calibri" panose="020F0502020204030204" pitchFamily="34" charset="0"/>
-              <a:ea typeface="Calibri" panose="020F0502020204030204" pitchFamily="34" charset="0"/>
-              <a:cs typeface="Calibri" panose="020F0502020204030204" pitchFamily="34" charset="0"/>
-            </a:rPr>
-            <a:t>NO6.</a:t>
-          </a:r>
-          <a:r>
-            <a:rPr lang="ja-JP" altLang="ja-JP" sz="1100">
-              <a:solidFill>
-                <a:schemeClr val="dk1"/>
-              </a:solidFill>
-              <a:effectLst/>
-              <a:latin typeface="Calibri" panose="020F0502020204030204" pitchFamily="34" charset="0"/>
-              <a:ea typeface="+mn-ea"/>
-              <a:cs typeface="Calibri" panose="020F0502020204030204" pitchFamily="34" charset="0"/>
-            </a:rPr>
-            <a:t>戻るボタンを押下して</a:t>
-          </a:r>
-          <a:r>
-            <a:rPr lang="ja-JP" altLang="en-US" sz="1100">
-              <a:solidFill>
-                <a:schemeClr val="dk1"/>
-              </a:solidFill>
-              <a:effectLst/>
-              <a:latin typeface="Calibri" panose="020F0502020204030204" pitchFamily="34" charset="0"/>
-              <a:ea typeface="+mn-ea"/>
-              <a:cs typeface="Calibri" panose="020F0502020204030204" pitchFamily="34" charset="0"/>
-            </a:rPr>
-            <a:t>加入者情報</a:t>
-          </a:r>
-          <a:r>
-            <a:rPr lang="ja-JP" altLang="ja-JP" sz="1100">
-              <a:solidFill>
-                <a:schemeClr val="dk1"/>
-              </a:solidFill>
-              <a:effectLst/>
-              <a:latin typeface="Calibri" panose="020F0502020204030204" pitchFamily="34" charset="0"/>
-              <a:ea typeface="+mn-ea"/>
-              <a:cs typeface="Calibri" panose="020F0502020204030204" pitchFamily="34" charset="0"/>
-            </a:rPr>
-            <a:t>検索画面にもどれる</a:t>
-          </a:r>
-          <a:endParaRPr lang="ja-JP" altLang="ja-JP">
-            <a:effectLst/>
-            <a:latin typeface="Calibri" panose="020F0502020204030204" pitchFamily="34" charset="0"/>
-            <a:cs typeface="Calibri" panose="020F0502020204030204" pitchFamily="34" charset="0"/>
-          </a:endParaRPr>
-        </a:p>
-        <a:p>
-          <a:pPr marL="0" marR="0" lvl="0" indent="0" algn="l" defTabSz="914400" eaLnBrk="1" fontAlgn="auto" latinLnBrk="0" hangingPunct="1">
-            <a:lnSpc>
-              <a:spcPct val="100000"/>
-            </a:lnSpc>
-            <a:spcBef>
-              <a:spcPts val="0"/>
-            </a:spcBef>
-            <a:spcAft>
-              <a:spcPts val="0"/>
-            </a:spcAft>
-            <a:buClrTx/>
-            <a:buSzTx/>
-            <a:buFontTx/>
-            <a:buNone/>
-            <a:tabLst/>
-            <a:defRPr/>
-          </a:pPr>
-          <a:endParaRPr kumimoji="1" lang="ja-JP" altLang="en-US" sz="1100"/>
-        </a:p>
-      </xdr:txBody>
-    </xdr:sp>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-</xdr:wsDr>
-</file>
-
-<file path=xl/drawings/drawing5.xml><?xml version="1.0" encoding="utf-8"?>
-<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-  <xdr:twoCellAnchor editAs="oneCell">
-    <xdr:from>
-      <xdr:col>1</xdr:col>
-      <xdr:colOff>0</xdr:colOff>
-      <xdr:row>3</xdr:row>
-      <xdr:rowOff>0</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>15</xdr:col>
-      <xdr:colOff>457200</xdr:colOff>
-      <xdr:row>11</xdr:row>
-      <xdr:rowOff>102374</xdr:rowOff>
-    </xdr:to>
-    <xdr:pic>
-      <xdr:nvPicPr>
-        <xdr:cNvPr id="3" name="図 2">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{0331387E-88CE-472A-8881-4CD806A3FA3D}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvPicPr>
-          <a:picLocks noChangeAspect="1"/>
-        </xdr:cNvPicPr>
-      </xdr:nvPicPr>
-      <xdr:blipFill>
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId1" cstate="print">
-          <a:extLst>
-            <a:ext uri="{28A0092B-C50C-407E-A947-70E740481C1C}">
-              <a14:useLocalDpi xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" val="0"/>
-            </a:ext>
-          </a:extLst>
-        </a:blip>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </xdr:blipFill>
-      <xdr:spPr>
-        <a:xfrm>
-          <a:off x="685800" y="514350"/>
-          <a:ext cx="10058400" cy="1473974"/>
-        </a:xfrm>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-      </xdr:spPr>
-    </xdr:pic>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-  <xdr:twoCellAnchor editAs="oneCell">
-    <xdr:from>
-      <xdr:col>17</xdr:col>
-      <xdr:colOff>1</xdr:colOff>
-      <xdr:row>3</xdr:row>
-      <xdr:rowOff>0</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>22</xdr:col>
-      <xdr:colOff>452658</xdr:colOff>
-      <xdr:row>24</xdr:row>
-      <xdr:rowOff>0</xdr:rowOff>
-    </xdr:to>
-    <xdr:pic>
-      <xdr:nvPicPr>
-        <xdr:cNvPr id="5" name="図 4">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{D53D42BC-D80F-4967-8227-822ADD165F6A}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvPicPr>
-          <a:picLocks noChangeAspect="1"/>
-        </xdr:cNvPicPr>
-      </xdr:nvPicPr>
-      <xdr:blipFill>
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId2">
-          <a:extLst>
-            <a:ext uri="{28A0092B-C50C-407E-A947-70E740481C1C}">
-              <a14:useLocalDpi xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" val="0"/>
-            </a:ext>
-          </a:extLst>
-        </a:blip>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </xdr:blipFill>
-      <xdr:spPr>
-        <a:xfrm>
-          <a:off x="11658601" y="514350"/>
-          <a:ext cx="3881657" cy="3600450"/>
-        </a:xfrm>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-      </xdr:spPr>
-    </xdr:pic>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-  <xdr:twoCellAnchor editAs="oneCell">
-    <xdr:from>
-      <xdr:col>1</xdr:col>
-      <xdr:colOff>0</xdr:colOff>
-      <xdr:row>27</xdr:row>
-      <xdr:rowOff>0</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>15</xdr:col>
-      <xdr:colOff>457200</xdr:colOff>
-      <xdr:row>35</xdr:row>
-      <xdr:rowOff>169194</xdr:rowOff>
-    </xdr:to>
-    <xdr:pic>
-      <xdr:nvPicPr>
-        <xdr:cNvPr id="7" name="図 6">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{D15F78EC-A612-4060-8841-1FB5B703628C}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvPicPr>
-          <a:picLocks noChangeAspect="1"/>
-        </xdr:cNvPicPr>
-      </xdr:nvPicPr>
-      <xdr:blipFill>
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId3" cstate="print">
-          <a:extLst>
-            <a:ext uri="{28A0092B-C50C-407E-A947-70E740481C1C}">
-              <a14:useLocalDpi xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" val="0"/>
-            </a:ext>
-          </a:extLst>
-        </a:blip>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </xdr:blipFill>
-      <xdr:spPr>
-        <a:xfrm>
-          <a:off x="685800" y="4629150"/>
-          <a:ext cx="10058400" cy="1540794"/>
-        </a:xfrm>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-      </xdr:spPr>
-    </xdr:pic>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-  <xdr:twoCellAnchor editAs="oneCell">
-    <xdr:from>
-      <xdr:col>17</xdr:col>
-      <xdr:colOff>1</xdr:colOff>
-      <xdr:row>26</xdr:row>
-      <xdr:rowOff>171449</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>22</xdr:col>
-      <xdr:colOff>523875</xdr:colOff>
-      <xdr:row>59</xdr:row>
-      <xdr:rowOff>170298</xdr:rowOff>
-    </xdr:to>
-    <xdr:pic>
-      <xdr:nvPicPr>
-        <xdr:cNvPr id="9" name="図 8">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{3AF8DB0E-45D8-40F0-AFE5-9BD1A9EE29D7}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvPicPr>
-          <a:picLocks noChangeAspect="1"/>
-        </xdr:cNvPicPr>
-      </xdr:nvPicPr>
-      <xdr:blipFill>
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId4">
-          <a:extLst>
-            <a:ext uri="{28A0092B-C50C-407E-A947-70E740481C1C}">
-              <a14:useLocalDpi xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" val="0"/>
-            </a:ext>
-          </a:extLst>
-        </a:blip>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </xdr:blipFill>
-      <xdr:spPr>
-        <a:xfrm>
-          <a:off x="11658601" y="4629149"/>
-          <a:ext cx="3952874" cy="5656699"/>
-        </a:xfrm>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-      </xdr:spPr>
-    </xdr:pic>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-  <xdr:twoCellAnchor editAs="oneCell">
-    <xdr:from>
-      <xdr:col>1</xdr:col>
-      <xdr:colOff>0</xdr:colOff>
-      <xdr:row>61</xdr:row>
-      <xdr:rowOff>0</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>15</xdr:col>
-      <xdr:colOff>457200</xdr:colOff>
-      <xdr:row>70</xdr:row>
-      <xdr:rowOff>52772</xdr:rowOff>
-    </xdr:to>
-    <xdr:pic>
-      <xdr:nvPicPr>
-        <xdr:cNvPr id="11" name="図 10">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{BC555D75-4D62-4A25-AFE0-0AD32F937B40}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvPicPr>
-          <a:picLocks noChangeAspect="1"/>
-        </xdr:cNvPicPr>
-      </xdr:nvPicPr>
-      <xdr:blipFill>
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId5" cstate="print">
-          <a:extLst>
-            <a:ext uri="{28A0092B-C50C-407E-A947-70E740481C1C}">
-              <a14:useLocalDpi xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" val="0"/>
-            </a:ext>
-          </a:extLst>
-        </a:blip>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </xdr:blipFill>
-      <xdr:spPr>
-        <a:xfrm>
-          <a:off x="685800" y="10458450"/>
-          <a:ext cx="10058400" cy="1595822"/>
-        </a:xfrm>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-      </xdr:spPr>
-    </xdr:pic>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-  <xdr:twoCellAnchor>
-    <xdr:from>
-      <xdr:col>4</xdr:col>
-      <xdr:colOff>390525</xdr:colOff>
-      <xdr:row>9</xdr:row>
-      <xdr:rowOff>66675</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>5</xdr:col>
-      <xdr:colOff>0</xdr:colOff>
-      <xdr:row>10</xdr:row>
-      <xdr:rowOff>123825</xdr:rowOff>
-    </xdr:to>
-    <xdr:sp macro="" textlink="">
-      <xdr:nvSpPr>
-        <xdr:cNvPr id="15" name="正方形/長方形 14">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{4B3C217B-5620-493C-8B54-6618C50F2974}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvSpPr/>
-      </xdr:nvSpPr>
-      <xdr:spPr>
-        <a:xfrm>
-          <a:off x="3133725" y="1609725"/>
-          <a:ext cx="295275" cy="228600"/>
-        </a:xfrm>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-        <a:noFill/>
-        <a:ln w="38100" cap="flat" cmpd="sng" algn="ctr">
-          <a:solidFill>
-            <a:srgbClr val="FF0000"/>
-          </a:solidFill>
-          <a:prstDash val="solid"/>
-          <a:round/>
-          <a:headEnd type="none" w="med" len="med"/>
-          <a:tailEnd type="none" w="med" len="med"/>
-        </a:ln>
-      </xdr:spPr>
-      <xdr:style>
-        <a:lnRef idx="0">
-          <a:scrgbClr r="0" g="0" b="0"/>
-        </a:lnRef>
-        <a:fillRef idx="0">
-          <a:scrgbClr r="0" g="0" b="0"/>
-        </a:fillRef>
-        <a:effectRef idx="0">
-          <a:scrgbClr r="0" g="0" b="0"/>
-        </a:effectRef>
-        <a:fontRef idx="minor">
-          <a:schemeClr val="accent2"/>
-        </a:fontRef>
-      </xdr:style>
-      <xdr:txBody>
-        <a:bodyPr vertOverflow="clip" horzOverflow="clip" rtlCol="0" anchor="t"/>
-        <a:lstStyle/>
-        <a:p>
-          <a:pPr algn="l"/>
-          <a:endParaRPr kumimoji="1" lang="ja-JP" altLang="en-US" sz="1100"/>
-        </a:p>
-      </xdr:txBody>
-    </xdr:sp>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-  <xdr:twoCellAnchor>
-    <xdr:from>
-      <xdr:col>4</xdr:col>
-      <xdr:colOff>485775</xdr:colOff>
-      <xdr:row>11</xdr:row>
-      <xdr:rowOff>19050</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>4</xdr:col>
-      <xdr:colOff>504825</xdr:colOff>
-      <xdr:row>25</xdr:row>
-      <xdr:rowOff>123825</xdr:rowOff>
-    </xdr:to>
-    <xdr:cxnSp macro="">
-      <xdr:nvCxnSpPr>
-        <xdr:cNvPr id="17" name="直線矢印コネクタ 16">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{4A3F4E6B-314D-47F4-BD2F-0BBEA2A39230}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvCxnSpPr/>
-      </xdr:nvCxnSpPr>
-      <xdr:spPr>
-        <a:xfrm flipH="1">
-          <a:off x="3228975" y="1905000"/>
-          <a:ext cx="19050" cy="2505075"/>
-        </a:xfrm>
-        <a:prstGeom prst="straightConnector1">
-          <a:avLst/>
-        </a:prstGeom>
-        <a:ln w="38100">
-          <a:solidFill>
-            <a:srgbClr val="FF0000"/>
-          </a:solidFill>
-          <a:tailEnd type="triangle"/>
-        </a:ln>
-      </xdr:spPr>
-      <xdr:style>
-        <a:lnRef idx="1">
-          <a:schemeClr val="accent1"/>
-        </a:lnRef>
-        <a:fillRef idx="0">
-          <a:schemeClr val="accent1"/>
-        </a:fillRef>
-        <a:effectRef idx="0">
-          <a:schemeClr val="accent1"/>
-        </a:effectRef>
-        <a:fontRef idx="minor">
-          <a:schemeClr val="tx1"/>
-        </a:fontRef>
-      </xdr:style>
-    </xdr:cxnSp>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-  <xdr:twoCellAnchor>
-    <xdr:from>
-      <xdr:col>4</xdr:col>
-      <xdr:colOff>390525</xdr:colOff>
-      <xdr:row>31</xdr:row>
-      <xdr:rowOff>28575</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>5</xdr:col>
-      <xdr:colOff>0</xdr:colOff>
-      <xdr:row>32</xdr:row>
-      <xdr:rowOff>85725</xdr:rowOff>
-    </xdr:to>
-    <xdr:sp macro="" textlink="">
-      <xdr:nvSpPr>
-        <xdr:cNvPr id="18" name="正方形/長方形 17">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{3B0D2B3B-6A44-4430-BD1F-35A060DAAA47}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvSpPr/>
-      </xdr:nvSpPr>
-      <xdr:spPr>
-        <a:xfrm>
-          <a:off x="3133725" y="5343525"/>
-          <a:ext cx="295275" cy="228600"/>
-        </a:xfrm>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-        <a:noFill/>
-        <a:ln w="38100" cap="flat" cmpd="sng" algn="ctr">
-          <a:solidFill>
-            <a:srgbClr val="FF0000"/>
-          </a:solidFill>
-          <a:prstDash val="solid"/>
-          <a:round/>
-          <a:headEnd type="none" w="med" len="med"/>
-          <a:tailEnd type="none" w="med" len="med"/>
-        </a:ln>
-      </xdr:spPr>
-      <xdr:style>
-        <a:lnRef idx="0">
-          <a:scrgbClr r="0" g="0" b="0"/>
-        </a:lnRef>
-        <a:fillRef idx="0">
-          <a:scrgbClr r="0" g="0" b="0"/>
-        </a:fillRef>
-        <a:effectRef idx="0">
-          <a:scrgbClr r="0" g="0" b="0"/>
-        </a:effectRef>
-        <a:fontRef idx="minor">
-          <a:schemeClr val="accent2"/>
-        </a:fontRef>
-      </xdr:style>
-      <xdr:txBody>
-        <a:bodyPr vertOverflow="clip" horzOverflow="clip" rtlCol="0" anchor="t"/>
-        <a:lstStyle/>
-        <a:p>
-          <a:pPr algn="l"/>
-          <a:endParaRPr kumimoji="1" lang="ja-JP" altLang="en-US" sz="1100"/>
-        </a:p>
-      </xdr:txBody>
-    </xdr:sp>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-  <xdr:twoCellAnchor>
-    <xdr:from>
-      <xdr:col>4</xdr:col>
-      <xdr:colOff>542925</xdr:colOff>
-      <xdr:row>33</xdr:row>
-      <xdr:rowOff>0</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>4</xdr:col>
-      <xdr:colOff>552450</xdr:colOff>
-      <xdr:row>60</xdr:row>
-      <xdr:rowOff>0</xdr:rowOff>
-    </xdr:to>
-    <xdr:cxnSp macro="">
-      <xdr:nvCxnSpPr>
-        <xdr:cNvPr id="19" name="直線矢印コネクタ 18">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{2EE743A1-5D21-49F6-B0E9-F1E755F35648}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvCxnSpPr/>
-      </xdr:nvCxnSpPr>
-      <xdr:spPr>
-        <a:xfrm flipH="1">
-          <a:off x="3286125" y="5657850"/>
-          <a:ext cx="9525" cy="4629150"/>
-        </a:xfrm>
-        <a:prstGeom prst="straightConnector1">
-          <a:avLst/>
-        </a:prstGeom>
-        <a:ln w="38100">
-          <a:solidFill>
-            <a:srgbClr val="FF0000"/>
-          </a:solidFill>
-          <a:tailEnd type="triangle"/>
-        </a:ln>
-      </xdr:spPr>
-      <xdr:style>
-        <a:lnRef idx="1">
-          <a:schemeClr val="accent1"/>
-        </a:lnRef>
-        <a:fillRef idx="0">
-          <a:schemeClr val="accent1"/>
-        </a:fillRef>
-        <a:effectRef idx="0">
-          <a:schemeClr val="accent1"/>
-        </a:effectRef>
-        <a:fontRef idx="minor">
-          <a:schemeClr val="tx1"/>
-        </a:fontRef>
-      </xdr:style>
-    </xdr:cxnSp>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-  <xdr:twoCellAnchor>
-    <xdr:from>
-      <xdr:col>7</xdr:col>
-      <xdr:colOff>127395</xdr:colOff>
-      <xdr:row>24</xdr:row>
-      <xdr:rowOff>82155</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>11</xdr:col>
-      <xdr:colOff>458390</xdr:colOff>
-      <xdr:row>29</xdr:row>
-      <xdr:rowOff>107158</xdr:rowOff>
-    </xdr:to>
-    <xdr:sp macro="" textlink="">
-      <xdr:nvSpPr>
-        <xdr:cNvPr id="22" name="吹き出し: 四角形 21">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{57903372-E62F-40FA-9DA8-75259CBA1D0B}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvSpPr/>
-      </xdr:nvSpPr>
-      <xdr:spPr>
-        <a:xfrm>
-          <a:off x="4919661" y="4225530"/>
-          <a:ext cx="3069432" cy="888206"/>
-        </a:xfrm>
-        <a:prstGeom prst="wedgeRectCallout">
-          <a:avLst>
-            <a:gd name="adj1" fmla="val -34798"/>
-            <a:gd name="adj2" fmla="val 73022"/>
-          </a:avLst>
-        </a:prstGeom>
-      </xdr:spPr>
-      <xdr:style>
-        <a:lnRef idx="2">
-          <a:schemeClr val="accent1"/>
-        </a:lnRef>
-        <a:fillRef idx="1">
-          <a:schemeClr val="lt1"/>
-        </a:fillRef>
-        <a:effectRef idx="0">
-          <a:schemeClr val="accent1"/>
-        </a:effectRef>
-        <a:fontRef idx="minor">
-          <a:schemeClr val="dk1"/>
-        </a:fontRef>
-      </xdr:style>
-      <xdr:txBody>
-        <a:bodyPr vertOverflow="clip" horzOverflow="clip" rtlCol="0" anchor="t"/>
-        <a:lstStyle/>
-        <a:p>
-          <a:pPr marL="0" marR="0" lvl="0" indent="0" algn="l" defTabSz="914400" eaLnBrk="1" fontAlgn="auto" latinLnBrk="0" hangingPunct="1">
-            <a:lnSpc>
-              <a:spcPct val="100000"/>
-            </a:lnSpc>
-            <a:spcBef>
-              <a:spcPts val="0"/>
-            </a:spcBef>
-            <a:spcAft>
-              <a:spcPts val="0"/>
-            </a:spcAft>
-            <a:buClrTx/>
-            <a:buSzTx/>
-            <a:buFontTx/>
-            <a:buNone/>
-            <a:tabLst/>
-            <a:defRPr/>
-          </a:pPr>
           <a:r>
             <a:rPr lang="ja-JP" altLang="ja-JP" sz="1100">
               <a:solidFill>
@@ -3455,11 +2675,104 @@
               <a:ea typeface="+mn-ea"/>
               <a:cs typeface="+mn-cs"/>
             </a:rPr>
-            <a:t>「メールアドレス」「氏名」両方に情報を入力して検索ボタンを押下したとき、入力した情報が加入者情報テーブルの「メールアドレス」「氏名」の両方に部分一致したユーザー情報を表示される</a:t>
+            <a:t>「メールアドレス」に</a:t>
           </a:r>
-        </a:p>
-        <a:p>
-          <a:pPr algn="l"/>
+          <a:r>
+            <a:rPr lang="en-US" altLang="ja-JP" sz="1100">
+              <a:solidFill>
+                <a:schemeClr val="dk1"/>
+              </a:solidFill>
+              <a:effectLst/>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:rPr>
+            <a:t>”b”</a:t>
+          </a:r>
+          <a:r>
+            <a:rPr lang="ja-JP" altLang="ja-JP" sz="1100">
+              <a:solidFill>
+                <a:schemeClr val="dk1"/>
+              </a:solidFill>
+              <a:effectLst/>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:rPr>
+            <a:t>「氏名」両方に“佐藤”と入力して検索ボタンを押下したとき、</a:t>
+          </a:r>
+          <a:r>
+            <a:rPr lang="en-US" altLang="ja-JP" sz="1100">
+              <a:solidFill>
+                <a:schemeClr val="dk1"/>
+              </a:solidFill>
+              <a:effectLst/>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:rPr>
+            <a:t>”b”</a:t>
+          </a:r>
+          <a:r>
+            <a:rPr lang="ja-JP" altLang="ja-JP" sz="1100">
+              <a:solidFill>
+                <a:schemeClr val="dk1"/>
+              </a:solidFill>
+              <a:effectLst/>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:rPr>
+            <a:t>と</a:t>
+          </a:r>
+          <a:r>
+            <a:rPr lang="en-US" altLang="ja-JP" sz="1100">
+              <a:solidFill>
+                <a:schemeClr val="dk1"/>
+              </a:solidFill>
+              <a:effectLst/>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:rPr>
+            <a:t>”</a:t>
+          </a:r>
+          <a:r>
+            <a:rPr lang="ja-JP" altLang="ja-JP" sz="1100">
+              <a:solidFill>
+                <a:schemeClr val="dk1"/>
+              </a:solidFill>
+              <a:effectLst/>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:rPr>
+            <a:t>佐藤</a:t>
+          </a:r>
+          <a:r>
+            <a:rPr lang="en-US" altLang="ja-JP" sz="1100">
+              <a:solidFill>
+                <a:schemeClr val="dk1"/>
+              </a:solidFill>
+              <a:effectLst/>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:rPr>
+            <a:t>”</a:t>
+          </a:r>
+          <a:r>
+            <a:rPr lang="ja-JP" altLang="ja-JP" sz="1100">
+              <a:solidFill>
+                <a:schemeClr val="dk1"/>
+              </a:solidFill>
+              <a:effectLst/>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:rPr>
+            <a:t>の両方に部分一致したユーザー情報が表示される</a:t>
+          </a:r>
           <a:endParaRPr kumimoji="1" lang="ja-JP" altLang="en-US" sz="1100"/>
         </a:p>
       </xdr:txBody>
@@ -3891,7 +3204,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{54B445FB-F118-47FF-BCA2-B773627F0ED9}">
-  <dimension ref="B2:B31"/>
+  <dimension ref="B2:B45"/>
   <sheetFormatPr defaultRowHeight="13.5" x14ac:dyDescent="0.15"/>
   <sheetData>
     <row r="2" spans="2:2" x14ac:dyDescent="0.15">
@@ -3912,6 +3225,14 @@
     <row r="31" spans="2:2" x14ac:dyDescent="0.15">
       <c r="B31" t="s">
         <v>4</v>
+      </c>
+    </row>
+    <row r="44" spans="2:2" ht="13.5" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="B44" s="2"/>
+    </row>
+    <row r="45" spans="2:2" x14ac:dyDescent="0.15">
+      <c r="B45" t="s">
+        <v>8</v>
       </c>
     </row>
   </sheetData>
@@ -3939,10 +3260,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="26" spans="2:39" x14ac:dyDescent="0.15">
-      <c r="B26" t="s">
-        <v>6</v>
-      </c>
+    <row r="26" spans="39:39" x14ac:dyDescent="0.15">
       <c r="AM26" t="s">
         <v>5</v>
       </c>
@@ -3962,18 +3280,15 @@
   <sheetData>
     <row r="2" spans="2:18" x14ac:dyDescent="0.15">
       <c r="B2" t="s">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="R2" t="s">
-        <v>8</v>
+        <v>6</v>
       </c>
     </row>
-    <row r="26" spans="2:18" x14ac:dyDescent="0.15">
-      <c r="B26" t="s">
-        <v>9</v>
-      </c>
+    <row r="26" spans="18:18" x14ac:dyDescent="0.15">
       <c r="R26" t="s">
-        <v>8</v>
+        <v>6</v>
       </c>
     </row>
   </sheetData>
@@ -3990,18 +3305,15 @@
   <sheetData>
     <row r="2" spans="2:18" x14ac:dyDescent="0.15">
       <c r="B2" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="R2" t="s">
-        <v>11</v>
+        <v>7</v>
       </c>
     </row>
-    <row r="25" spans="2:18" x14ac:dyDescent="0.15">
-      <c r="B25" t="s">
-        <v>12</v>
-      </c>
+    <row r="25" spans="18:18" x14ac:dyDescent="0.15">
       <c r="R25" t="s">
-        <v>11</v>
+        <v>7</v>
       </c>
     </row>
   </sheetData>
@@ -4018,21 +3330,18 @@
   <sheetData>
     <row r="2" spans="2:18" x14ac:dyDescent="0.15">
       <c r="B2" t="s">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="R2" t="s">
-        <v>11</v>
+        <v>7</v>
       </c>
     </row>
     <row r="16" spans="2:18" x14ac:dyDescent="0.15">
       <c r="H16" s="1"/>
     </row>
-    <row r="26" spans="2:18" x14ac:dyDescent="0.15">
-      <c r="B26" t="s">
-        <v>14</v>
-      </c>
+    <row r="26" spans="18:18" x14ac:dyDescent="0.15">
       <c r="R26" t="s">
-        <v>11</v>
+        <v>7</v>
       </c>
     </row>
   </sheetData>
@@ -4043,21 +3352,6 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement/>
-</p:properties>
-</file>
-
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
-</file>
-
-<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="ドキュメント" ma:contentTypeID="0x010100C424317A42AA8449A97AAE94730ED181" ma:contentTypeVersion="6" ma:contentTypeDescription="新しいドキュメントを作成します。" ma:contentTypeScope="" ma:versionID="9df5c7ff725c9e365f8a8503f6029c6b">
   <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="dab87824-9c6b-4a08-9c96-9c9ea904f12c" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="98e3d8fd3bbedc5b58bd9df00d6be37e" ns2:_="">
     <xsd:import namespace="dab87824-9c6b-4a08-9c96-9c9ea904f12c"/>
@@ -4215,31 +3509,22 @@
 </ct:contentTypeSchema>
 </file>
 
-<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{F8048152-0CA9-47E5-A6CC-6D3980A2E781}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
-    <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
-    <ds:schemaRef ds:uri="dab87824-9c6b-4a08-9c96-9c9ea904f12c"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/dcmitype/"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
-    <ds:schemaRef ds:uri="http://www.w3.org/XML/1998/namespace"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
 </file>
 
-<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{25A96F8A-B775-40FD-BBE8-4BBDAB58FCAE}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
+<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement/>
+</p:properties>
 </file>
 
-<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{EFE06169-F6B9-4EE2-B032-3DCCE6AFCC5C}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
@@ -4255,4 +3540,28 @@
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/internal/obd"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
+</file>
+
+<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{25A96F8A-B775-40FD-BBE8-4BBDAB58FCAE}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
+</file>
+
+<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{F8048152-0CA9-47E5-A6CC-6D3980A2E781}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
+    <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
+    <ds:schemaRef ds:uri="dab87824-9c6b-4a08-9c96-9c9ea904f12c"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/dcmitype/"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="http://www.w3.org/XML/1998/namespace"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>